--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -661,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -689,10 +690,11 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>· ③ 인터넷+TV 사은품: 종류 / SK-매장 / SK-온라인 / KT-매장 / KT-온라인 / LG-매장 / LG-온라인 / 비고</t>
-        </is>
-      </c>
-    </row>
+          <t>· ③ 인터넷+TV 사은품: 종류 / SK / KT / LG / 비고 (통합 1개 · 온·오프라인 공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -721,10 +723,11 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 인터넷+TV 사은품 1행 (3사 × 2채널 = 6칸)</t>
-        </is>
-      </c>
-    </row>
+          <t>· 인터넷+TV 사은품 1행 (3사 컬럼 · 통합 1개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -757,6 +760,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -797,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -2435,23 +2440,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 · 통신사 × 채널별 금액</t>
+          <t>📡 인터넷+TV 사은품 · 3사 통합 1개 (온·오프라인 공통)</t>
         </is>
       </c>
     </row>
@@ -2463,35 +2465,20 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>SK-매장</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>SK-온라인</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>KT-매장</t>
-        </is>
-      </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>KT-온라인</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>LG-매장</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>LG-온라인</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2506,22 +2493,13 @@
       <c r="B3" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" s="23" t="n">
+      <c r="C3" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="24" t="n">
+      <c r="D3" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="G3" s="24" t="n">
-        <v>45</v>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>만원 · 샘플</t>
         </is>
@@ -2530,14 +2508,14 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 현금 페이백 · 통신사 × 채널(매장/온라인)별 금액 · 단위: 만원 · 샘플 값 입력됨</t>
+          <t>※ 인터넷+TV 정책은 온·오프라인 통합 1개 (매트릭스 참조) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -129,56 +129,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00dc2626"/>
+        <bgColor rgb="00dc2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002563eb"/>
         <bgColor rgb="002563eb"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00059669"/>
-        <bgColor rgb="00059669"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00eff6ff"/>
-        <bgColor rgb="00eff6ff"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f0fdf4"/>
-        <bgColor rgb="00f0fdf4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00dc2626"/>
-        <bgColor rgb="00dc2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00991b1b"/>
-        <bgColor rgb="00991b1b"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001e40af"/>
-        <bgColor rgb="001e40af"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00e40981"/>
         <bgColor rgb="00e40981"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009d174d"/>
-        <bgColor rgb="009d174d"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -252,25 +216,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -647,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -657,16 +603,15 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>봉이모바일 공통폼 템플릿 (오프라인+온라인 통합)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>봉이모바일 공통폼 템플릿 (매장/온라인 공용)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>📌 컬럼 구조</t>
+          <t>📌 공통폼</t>
         </is>
       </c>
     </row>
@@ -674,7 +619,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>· ① 무선: 통신사 / 펫네임 / 요금제(월요금) / 번이 / 기변 (오프라인·온라인 공통 · 값 동일)</t>
+          <t>· 한 개 템플릿 파일을 오프라인(12개 매장)과 온라인(1개 통합)이 각자 복사해서 사용</t>
         </is>
       </c>
     </row>
@@ -682,7 +627,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>· ② 유심: 통신사 / 요금제(월요금) / 25%↓실납 / 번이-매장 / 번이-온라인</t>
+          <t>· 구조 동일 · 매장/온라인이 자기 채널 값만 입력</t>
         </is>
       </c>
     </row>
@@ -690,16 +635,15 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>· ③ 인터넷+TV 사은품: 종류 / SK / KT / LG / 비고 (통합 1개 · 온·오프라인 공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>· 저장 시 파일명 구분 (예: template-form-상무점.xlsx / template-form-온라인.xlsx)</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>📊 데이터</t>
+          <t>📊 시트 구조</t>
         </is>
       </c>
     </row>
@@ -707,7 +651,7 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>· 무선 54행 (정리3 원본)</t>
+          <t>· ① 무선(휴대폰): 통신사/펫네임/요금제(월요금)/번이/기변 · 54행</t>
         </is>
       </c>
     </row>
@@ -715,7 +659,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 유심 9행 (매장·온라인 페이백 한 행에 병렬 표기)</t>
+          <t>· ② 유심: 통신사/요금제(월요금)/25%↓실납/번이 · 9행</t>
         </is>
       </c>
     </row>
@@ -723,11 +667,10 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 인터넷+TV 사은품 1행 (3사 컬럼 · 통합 1개)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>· ③ 인터넷+TV 사은품: 종류/SK/KT/LG/비고 · 1행 (통합 1개 · 온·오프라인 공통)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -760,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -781,7 +723,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75</t>
+          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
         </is>
       </c>
     </row>
@@ -801,7 +743,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -822,7 +763,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· 매장 컬럼(파란 배경) = 오프라인 12개 매장 공통 적용</t>
+          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 사은품=(종류)</t>
         </is>
       </c>
     </row>
@@ -830,15 +771,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· 온라인 컬럼(초록 배경) = 온라인 통합 1개 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 새 기종/요금제는 행 추가</t>
+          <t>· 샘플 값 입력됨 → 실제 정책으로 덮어쓰기</t>
         </is>
       </c>
     </row>
@@ -856,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -869,7 +802,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📱 무선(휴대폰) 시세 · 54행 (오프라인·온라인 공통)</t>
+          <t>📱 무선(휴대폰) 시세 · 54행</t>
         </is>
       </c>
     </row>
@@ -2142,17 +2075,19 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강) · 오프라인/온라인 값 동일</t>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
+※ 새 기종은 행 추가 · 컬럼 고정</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A57:E57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2164,20 +2099,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 · 9행 · 매장/온라인 병렬</t>
+          <t>📇 유심 시세 · 9행 (샘플 값 포함)</t>
         </is>
       </c>
     </row>
@@ -2197,14 +2131,9 @@
           <t>25%↓실납</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>번이-매장</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>번이-온라인</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>번이</t>
         </is>
       </c>
     </row>
@@ -2224,11 +2153,8 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="8" t="n">
         <v>-40</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>-25</v>
       </c>
     </row>
     <row r="4">
@@ -2247,11 +2173,8 @@
           <t>33,750</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="8" t="n">
         <v>-35</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>-30</v>
       </c>
     </row>
     <row r="5">
@@ -2270,11 +2193,8 @@
           <t>41,250</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="8" t="n">
         <v>-40</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>-35</v>
       </c>
     </row>
     <row r="6">
@@ -2293,11 +2213,8 @@
           <t>27,750</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="8" t="n">
         <v>-15</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-5</v>
       </c>
     </row>
     <row r="7">
@@ -2316,11 +2233,8 @@
           <t>37,500</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="8" t="n">
         <v>-20</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-10</v>
       </c>
     </row>
     <row r="8">
@@ -2339,11 +2253,8 @@
           <t>51,750</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="8" t="n">
         <v>-25</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-15</v>
       </c>
     </row>
     <row r="9">
@@ -2362,10 +2273,7 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="8" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -2385,11 +2293,8 @@
           <t>45,750</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="8" t="n">
         <v>-30</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-25</v>
       </c>
     </row>
     <row r="11">
@@ -2408,27 +2313,24 @@
           <t>63,750</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="E11" s="16" t="n">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>※ 유심은 MNP 전용 · 펫네임/기변 없음 · 번이 만원 · 음수=페이백
-※ 번이-매장 (파란 배경) = 오프라인 12개 매장 공통 적용 · 번이-온라인 (초록 배경) = 온라인 통합
-※ 실납 = 월요금 × 0.75 (선택약정 25% · SK/KT 개통시 · LG 개통 후 고객센터)
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이(만원)만 입력
+※ 실납 = 월요금 × 0.75 (선택약정 25% 할인 · SK/KT 개통시 · LG 개통 후 고객센터 신청)
+※ 샘플 값 입력됨 — 매장/온라인이 각자 자기 페이백 값으로 덮어쓰기
 ※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2453,7 +2355,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 · 3사 통합 1개 (온·오프라인 공통)</t>
+          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통)</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2365,17 @@
           <t>종류</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2490,13 +2392,13 @@
           <t>현금</t>
         </is>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="D3" s="24" t="n">
+      <c r="D3" s="18" t="n">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -2508,7 +2410,7 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 인터넷+TV 정책은 온·오프라인 통합 1개 (매트릭스 참조) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
+          <t>※ 인터넷+TV 정책은 매트릭스 기준 통합 1개 (온·오프라인 공통) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
         </is>
       </c>
     </row>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -172,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -226,6 +228,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -607,6 +612,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -639,6 +645,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -671,6 +678,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -703,6 +711,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -743,6 +752,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +85,46 @@
       <color rgb="0078350f"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006366f1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00059669"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400e"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00be185d"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006b7280"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +185,31 @@
         <bgColor rgb="00e40981"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001f2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fee2e2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dbeafe"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fce7f3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -174,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +296,34 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -612,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -645,7 +735,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -678,7 +767,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -711,7 +799,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -752,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -2352,82 +2438,1510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>종류</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통) · 63개 상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>통신사</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>상품 구성</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>사은품(원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>현금</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E58" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="D3" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>만원 · 샘플</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>※ 인터넷+TV 정책은 매트릭스 기준 통합 1개 (온·오프라인 공통) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E62" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>※ 인터넷+TV 사은품 정책은 통합 1개 (온·오프라인 공통) · 매장별 차등 없음 · 단위: 원</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A66:E66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📋 안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="① 무선(휴대폰)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="② 유심" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="③ 인터넷+TV 사은품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 무선(휴대폰)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 유심" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 인터넷+TV 사은품" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,8 +123,60 @@
       <color rgb="006b7280"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003617CE"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003617CE"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A2744"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -210,8 +262,62 @@
         <fgColor rgb="00fce7f3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+        <bgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B45309"/>
+        <bgColor rgb="00B45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -233,11 +339,25 @@
         <color rgb="00cccccc"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -324,6 +444,57 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -689,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -747,7 +918,7 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>· ① 무선(휴대폰): 통신사/펫네임/요금제(월요금)/번이/기변 · 54행</t>
+          <t>· ① 무선(휴대폰): 통신사/펫네임/용량/출고가/요금제/공시/번이 현금가/기변 현금가 (입력 8) + 봉이지원금 자동 2 · 54행</t>
         </is>
       </c>
     </row>
@@ -763,7 +934,7 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· ③ 인터넷+TV 사은품: 종류/SK/KT/LG/비고 · 1행 (통합 1개 · 온·오프라인 공통)</t>
+          <t>· ③ 인터넷+TV 사은품: 종류/SK/KT/LG/비고 · 63행 (통합 1개 · 온·오프라인 공통)</t>
         </is>
       </c>
     </row>
@@ -851,7 +1022,7 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>· 값 단위: 만원 · 음수=페이백(초록) · 양수=부담(빨강)</t>
+          <t>· 값 단위: 만원 · 현금가 음수 허용 (매장이 고객에 현금 페이백 = 봉이지원금 증가)</t>
         </is>
       </c>
     </row>
@@ -859,7 +1030,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 사은품=(종류)</t>
+          <t>· PK: 무선=(통신사+펫네임+용량+요금제) · 유심=(통신사+요금제) · 사은품=(#)</t>
         </is>
       </c>
     </row>
@@ -867,7 +1038,136 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· 샘플 값 입력됨 → 실제 정책으로 덮어쓰기</t>
+          <t>· 입력 컬럼만 수정 · 봉이지원금(I·J)은 자동 계산 — 수동 입력 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>💡 봉이 거래 공식 — 봉이지원금(역산) = 할부 페이백</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>【공시지원금 케이스】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>· 현금: 출고가 − 공시 − 봉이지원금 = 현금가</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>· 할부: 봉이지원금 = 할부 페이백 (개통 14일 후 별도 현금 지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>· 예①: 180 − 50 − 봉이지원금 = 10  → 봉이지원금 = 120만</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>· 예②: 180 − 50 − 봉이지원금 = −10 → 봉이지원금 = 140만 (현금가 음수 → 봉이가 매장에 더 보상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>【선택약정 25% 케이스】</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>· 현금: 출고가 − 봉이지원금 = 선약 현금가 (공시지원금 미적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>· 할부: 봉이지원금 = 선약 할부 페이백</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>· 예: 180 − 봉이지원금 = 30 → 봉이지원금 = 150만 / + 월 요금 25%↓ 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>🧮 ① 무선 시트 자동 계산 (공시 케이스 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>· I (번이 봉이지원금=할부페이백) = D − F − G</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>· J (기변 봉이지원금=할부페이백) = D − F − H</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>· 선약 케이스는 F열을 0으로 임시 변경 후 동일 컬럼 사용 (또는 별도 행 입력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>📝 입력 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>· 현금가는 음수 허용 (음수 = 매장이 고객에 추가 현금 페이백)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>· 매장이 현금가만 입력하면 봉이지원금/할부 페이백 자동 산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>· 할부 24개월 / 수수료 5.9% 원리금균등 별도 / 공시·선약 동시 적용 불가</t>
         </is>
       </c>
     </row>
@@ -885,1305 +1185,2380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>📱 무선(휴대폰) 시세 · 54행</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>📱 무선(휴대폰) 시세 · 54행 · 입력=현금가 / 자동=봉이지원금(역산=할부 페이백)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>통신사</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>펫네임</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>용량</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
+        <is>
+          <t>출고가
+(만원)</t>
+        </is>
+      </c>
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>요금제(월요금)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>번이</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>기변</t>
+      <c r="F2" s="32" t="inlineStr">
+        <is>
+          <t>공시지원금
+(만원)</t>
+        </is>
+      </c>
+      <c r="G2" s="32" t="inlineStr">
+        <is>
+          <t>번이 현금가
+(만원·입력)</t>
+        </is>
+      </c>
+      <c r="H2" s="32" t="inlineStr">
+        <is>
+          <t>기변 현금가
+(만원·입력)</t>
+        </is>
+      </c>
+      <c r="I2" s="45" t="inlineStr">
+        <is>
+          <t>봉이지원금=할부페이백
+(번이·만원·자동)</t>
+        </is>
+      </c>
+      <c r="J2" s="45" t="inlineStr">
+        <is>
+          <t>봉이지원금=할부페이백
+(기변·만원·자동)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>S26</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="F3" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="46" t="n">
         <v>-10</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="H3" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="I3" s="47">
+        <f>D3-F3-G3</f>
+        <v/>
+      </c>
+      <c r="J3" s="47">
+        <f>D3-F3-H3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>S26+</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>145</v>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="F4" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="H4" s="46" t="n">
         <v>34</v>
       </c>
+      <c r="I4" s="47">
+        <f>D4-F4-G4</f>
+        <v/>
+      </c>
+      <c r="J4" s="47">
+        <f>D4-F4-H4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>S26U</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>180</v>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="F5" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" s="46" t="n">
         <v>44</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="H5" s="46" t="n">
         <v>64</v>
       </c>
+      <c r="I5" s="47">
+        <f>D5-F5-G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="47">
+        <f>D5-F5-H5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>플립7</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="F6" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" s="46" t="n">
         <v>19</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="H6" s="46" t="n">
         <v>44</v>
       </c>
+      <c r="I6" s="47">
+        <f>D6-F6-G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="47">
+        <f>D6-F6-H6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>폴드7</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>230</v>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="F7" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" s="46" t="n">
         <v>127</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="H7" s="46" t="n">
         <v>139</v>
       </c>
+      <c r="I7" s="47">
+        <f>D7-F7-G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="47">
+        <f>D7-F7-H7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>S25</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>115</v>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="F8" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="H8" s="46" t="n">
         <v>59</v>
       </c>
+      <c r="I8" s="47">
+        <f>D8-F8-G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="47">
+        <f>D8-F8-H8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>S25+</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="F9" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" s="46" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="H9" s="46" t="n">
         <v>79</v>
       </c>
+      <c r="I9" s="47">
+        <f>D9-F9-G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="47">
+        <f>D9-F9-H9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>S25U</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="F10" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" s="46" t="n">
         <v>59</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="H10" s="46" t="n">
         <v>114</v>
       </c>
+      <c r="I10" s="47">
+        <f>D10-F10-G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="47">
+        <f>D10-F10-H10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>S25엣지</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="F11" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" s="46" t="n">
         <v>39</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="H11" s="46" t="n">
         <v>37</v>
       </c>
+      <c r="I11" s="47">
+        <f>D11-F11-G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="47">
+        <f>D11-F11-H11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>S25 FE</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="F12" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G12" s="46" t="n">
         <v>-35</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="H12" s="46" t="n">
         <v>-5</v>
       </c>
+      <c r="I12" s="47">
+        <f>D12-F12-G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="47">
+        <f>D12-F12-H12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>아이폰16</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="F13" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G13" s="46" t="n">
         <v>19</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="H13" s="46" t="n">
         <v>59</v>
       </c>
+      <c r="I13" s="47">
+        <f>D13-F13-G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="47">
+        <f>D13-F13-H13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>아이폰16 플러스</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="F14" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G14" s="46" t="n">
         <v>74</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="H14" s="46" t="n">
         <v>79</v>
       </c>
+      <c r="I14" s="47">
+        <f>D14-F14-G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="47">
+        <f>D14-F14-H14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="F15" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G15" s="46" t="n">
         <v>49</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="H15" s="46" t="n">
         <v>79</v>
       </c>
+      <c r="I15" s="47">
+        <f>D15-F15-G15</f>
+        <v/>
+      </c>
+      <c r="J15" s="47">
+        <f>D15-F15-H15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="F16" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" s="46" t="n">
         <v>124</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="H16" s="46" t="n">
         <v>129</v>
       </c>
+      <c r="I16" s="47">
+        <f>D16-F16-G16</f>
+        <v/>
+      </c>
+      <c r="J16" s="47">
+        <f>D16-F16-H16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>아이폰 17</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="F17" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G17" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="H17" s="46" t="n">
         <v>54</v>
       </c>
+      <c r="I17" s="47">
+        <f>D17-F17-G17</f>
+        <v/>
+      </c>
+      <c r="J17" s="47">
+        <f>D17-F17-H17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>아이폰17 AIR</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="F18" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G18" s="46" t="n">
         <v>49</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="H18" s="46" t="n">
         <v>84</v>
       </c>
+      <c r="I18" s="47">
+        <f>D18-F18-G18</f>
+        <v/>
+      </c>
+      <c r="J18" s="47">
+        <f>D18-F18-H18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>아이폰17 PRO</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>175</v>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="F19" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" s="46" t="n">
         <v>59</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="H19" s="46" t="n">
         <v>104</v>
       </c>
+      <c r="I19" s="47">
+        <f>D19-F19-G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="47">
+        <f>D19-F19-H19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>아이폰17 프로맥스</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>프리미엄(125,000)</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="F20" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="G20" s="46" t="n">
         <v>109</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="H20" s="46" t="n">
         <v>144</v>
       </c>
+      <c r="I20" s="47">
+        <f>D20-F20-G20</f>
+        <v/>
+      </c>
+      <c r="J20" s="47">
+        <f>D20-F20-H20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>S26</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="F21" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" s="46" t="n">
         <v>-20</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="H21" s="46" t="n">
         <v>-15</v>
       </c>
+      <c r="I21" s="47">
+        <f>D21-F21-G21</f>
+        <v/>
+      </c>
+      <c r="J21" s="47">
+        <f>D21-F21-H21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>S26+</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>145</v>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="F22" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="H22" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="I22" s="47">
+        <f>D22-F22-G22</f>
+        <v/>
+      </c>
+      <c r="J22" s="47">
+        <f>D22-F22-H22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>S26U</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>180</v>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="F23" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="H23" s="46" t="n">
         <v>39</v>
       </c>
+      <c r="I23" s="47">
+        <f>D23-F23-G23</f>
+        <v/>
+      </c>
+      <c r="J23" s="47">
+        <f>D23-F23-H23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>플립7</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="F24" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="H24" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="I24" s="47">
+        <f>D24-F24-G24</f>
+        <v/>
+      </c>
+      <c r="J24" s="47">
+        <f>D24-F24-H24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>폴드7</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>230</v>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="F25" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="46" t="n">
         <v>99</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="H25" s="46" t="n">
         <v>104</v>
       </c>
+      <c r="I25" s="47">
+        <f>D25-F25-G25</f>
+        <v/>
+      </c>
+      <c r="J25" s="47">
+        <f>D25-F25-H25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>S25</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>115</v>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="F26" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="H26" s="46" t="n">
         <v>19</v>
       </c>
+      <c r="I26" s="47">
+        <f>D26-F26-G26</f>
+        <v/>
+      </c>
+      <c r="J26" s="47">
+        <f>D26-F26-H26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>S25+</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="F27" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="46" t="n">
         <v>19</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="H27" s="46" t="n">
         <v>39</v>
       </c>
+      <c r="I27" s="47">
+        <f>D27-F27-G27</f>
+        <v/>
+      </c>
+      <c r="J27" s="47">
+        <f>D27-F27-H27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>S25U</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="F28" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" s="46" t="n">
         <v>54</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="H28" s="46" t="n">
         <v>74</v>
       </c>
+      <c r="I28" s="47">
+        <f>D28-F28-G28</f>
+        <v/>
+      </c>
+      <c r="J28" s="47">
+        <f>D28-F28-H28</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>S25엣지</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="F29" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="H29" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="I29" s="47">
+        <f>D29-F29-G29</f>
+        <v/>
+      </c>
+      <c r="J29" s="47">
+        <f>D29-F29-H29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>S25 FE</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="F30" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" s="46" t="n">
         <v>-40</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="H30" s="46" t="n">
         <v>-25</v>
       </c>
+      <c r="I30" s="47">
+        <f>D30-F30-G30</f>
+        <v/>
+      </c>
+      <c r="J30" s="47">
+        <f>D30-F30-H30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>아이폰16</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="F31" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="46" t="n">
         <v>-55</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="H31" s="46" t="n">
         <v>-30</v>
       </c>
+      <c r="I31" s="47">
+        <f>D31-F31-G31</f>
+        <v/>
+      </c>
+      <c r="J31" s="47">
+        <f>D31-F31-H31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>아이폰16 플러스</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="F32" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="46" t="n">
         <v>-45</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="H32" s="46" t="n">
         <v>-20</v>
       </c>
+      <c r="I32" s="47">
+        <f>D32-F32-G32</f>
+        <v/>
+      </c>
+      <c r="J32" s="47">
+        <f>D32-F32-H32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="F33" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="46" t="n">
         <v>-25</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="H33" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="I33" s="47">
+        <f>D33-F33-G33</f>
+        <v/>
+      </c>
+      <c r="J33" s="47">
+        <f>D33-F33-H33</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="F34" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="H34" s="46" t="n">
         <v>34</v>
       </c>
+      <c r="I34" s="47">
+        <f>D34-F34-G34</f>
+        <v/>
+      </c>
+      <c r="J34" s="47">
+        <f>D34-F34-H34</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>아이폰 17</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="F35" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="46" t="n">
         <v>-5</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="H35" s="46" t="n">
         <v>24</v>
       </c>
+      <c r="I35" s="47">
+        <f>D35-F35-G35</f>
+        <v/>
+      </c>
+      <c r="J35" s="47">
+        <f>D35-F35-H35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>아이폰17 AIR</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="F36" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="H36" s="46" t="n">
         <v>54</v>
       </c>
+      <c r="I36" s="47">
+        <f>D36-F36-G36</f>
+        <v/>
+      </c>
+      <c r="J36" s="47">
+        <f>D36-F36-H36</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>아이폰17 PRO</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>175</v>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="F37" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" s="46" t="n">
         <v>59</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="H37" s="46" t="n">
         <v>79</v>
       </c>
+      <c r="I37" s="47">
+        <f>D37-F37-G37</f>
+        <v/>
+      </c>
+      <c r="J37" s="47">
+        <f>D37-F37-H37</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>아이폰17 프로맥스</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>초이스스페셜(130,000)</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="F38" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="46" t="n">
         <v>94</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="H38" s="46" t="n">
         <v>124</v>
       </c>
+      <c r="I38" s="47">
+        <f>D38-F38-G38</f>
+        <v/>
+      </c>
+      <c r="J38" s="47">
+        <f>D38-F38-H38</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>S26</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="F39" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G39" s="46" t="n">
         <v>-25</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="H39" s="46" t="n">
         <v>-20</v>
       </c>
+      <c r="I39" s="47">
+        <f>D39-F39-G39</f>
+        <v/>
+      </c>
+      <c r="J39" s="47">
+        <f>D39-F39-H39</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>S26+</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>145</v>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="F40" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G40" s="46" t="n">
         <v>-5</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="H40" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="I40" s="47">
+        <f>D40-F40-G40</f>
+        <v/>
+      </c>
+      <c r="J40" s="47">
+        <f>D40-F40-H40</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>S26U</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>180</v>
+      </c>
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="F41" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G41" s="46" t="n">
         <v>29</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="H41" s="46" t="n">
         <v>34</v>
       </c>
+      <c r="I41" s="47">
+        <f>D41-F41-G41</f>
+        <v/>
+      </c>
+      <c r="J41" s="47">
+        <f>D41-F41-H41</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>플립7</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="F42" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G42" s="46" t="n">
         <v>-5</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="H42" s="46" t="n">
         <v>-5</v>
       </c>
+      <c r="I42" s="47">
+        <f>D42-F42-G42</f>
+        <v/>
+      </c>
+      <c r="J42" s="47">
+        <f>D42-F42-H42</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>폴드7</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="n">
+        <v>230</v>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="F43" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G43" s="46" t="n">
         <v>94</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="H43" s="46" t="n">
         <v>94</v>
       </c>
+      <c r="I43" s="47">
+        <f>D43-F43-G43</f>
+        <v/>
+      </c>
+      <c r="J43" s="47">
+        <f>D43-F43-H43</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>S25</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>115</v>
+      </c>
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="F44" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G44" s="46" t="n">
         <v>19</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="H44" s="46" t="n">
         <v>24</v>
       </c>
+      <c r="I44" s="47">
+        <f>D44-F44-G44</f>
+        <v/>
+      </c>
+      <c r="J44" s="47">
+        <f>D44-F44-H44</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>S25+</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="F45" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G45" s="46" t="n">
         <v>39</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="H45" s="46" t="n">
         <v>44</v>
       </c>
+      <c r="I45" s="47">
+        <f>D45-F45-G45</f>
+        <v/>
+      </c>
+      <c r="J45" s="47">
+        <f>D45-F45-H45</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>S25U</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="F46" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G46" s="46" t="n">
         <v>74</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="H46" s="46" t="n">
         <v>78</v>
       </c>
+      <c r="I46" s="47">
+        <f>D46-F46-G46</f>
+        <v/>
+      </c>
+      <c r="J46" s="47">
+        <f>D46-F46-H46</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>S25엣지</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E47" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="F47" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G47" s="46" t="n">
         <v>-20</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="H47" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="I47" s="47">
+        <f>D47-F47-G47</f>
+        <v/>
+      </c>
+      <c r="J47" s="47">
+        <f>D47-F47-H47</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>S25 FE</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D48" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="F48" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G48" s="46" t="n">
         <v>-50</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="H48" s="46" t="n">
         <v>-15</v>
       </c>
+      <c r="I48" s="47">
+        <f>D48-F48-G48</f>
+        <v/>
+      </c>
+      <c r="J48" s="47">
+        <f>D48-F48-H48</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="33" t="inlineStr">
         <is>
           <t>아이폰16</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="F49" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G49" s="46" t="n">
         <v>-40</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="H49" s="46" t="n">
         <v>14</v>
       </c>
+      <c r="I49" s="47">
+        <f>D49-F49-G49</f>
+        <v/>
+      </c>
+      <c r="J49" s="47">
+        <f>D49-F49-H49</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>아이폰16 플러스</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D50" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="F50" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="H50" s="46" t="n">
         <v>54</v>
       </c>
+      <c r="I50" s="47">
+        <f>D50-F50-G50</f>
+        <v/>
+      </c>
+      <c r="J50" s="47">
+        <f>D50-F50-H50</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D51" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="F51" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G51" s="46" t="n">
         <v>-5</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="H51" s="46" t="n">
         <v>44</v>
       </c>
+      <c r="I51" s="47">
+        <f>D51-F51-G51</f>
+        <v/>
+      </c>
+      <c r="J51" s="47">
+        <f>D51-F51-H51</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>아이폰16 프로맥스 256G</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="F52" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G52" s="46" t="n">
         <v>29</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="H52" s="46" t="n">
         <v>84</v>
       </c>
+      <c r="I52" s="47">
+        <f>D52-F52-G52</f>
+        <v/>
+      </c>
+      <c r="J52" s="47">
+        <f>D52-F52-H52</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>아이폰 17</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D53" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="F53" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G53" s="46" t="n">
         <v>-15</v>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="H53" s="46" t="n">
         <v>19</v>
       </c>
+      <c r="I53" s="47">
+        <f>D53-F53-G53</f>
+        <v/>
+      </c>
+      <c r="J53" s="47">
+        <f>D53-F53-H53</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>아이폰17 AIR</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D54" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
+      <c r="F54" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G54" s="46" t="n">
         <v>-40</v>
       </c>
-      <c r="E54" s="9" t="n">
+      <c r="H54" s="46" t="n">
         <v>49</v>
       </c>
+      <c r="I54" s="47">
+        <f>D54-F54-G54</f>
+        <v/>
+      </c>
+      <c r="J54" s="47">
+        <f>D54-F54-H54</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="33" t="inlineStr">
         <is>
           <t>아이폰17 PRO</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D55" s="33" t="n">
+        <v>175</v>
+      </c>
+      <c r="E55" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D55" s="9" t="n">
+      <c r="F55" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G55" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="E55" s="9" t="n">
+      <c r="H55" s="46" t="n">
         <v>69</v>
       </c>
+      <c r="I55" s="47">
+        <f>D55-F55-G55</f>
+        <v/>
+      </c>
+      <c r="J55" s="47">
+        <f>D55-F55-H55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="33" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>아이폰17 프로맥스</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>512GB</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>프리미어 슈퍼(125,000)</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="F56" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="G56" s="46" t="n">
         <v>89</v>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="H56" s="46" t="n">
         <v>114</v>
       </c>
-    </row>
-    <row r="58" ht="80" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
-※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
-※ 새 기종은 행 추가 · 컬럼 고정</t>
+      <c r="I56" s="47">
+        <f>D56-F56-G56</f>
+        <v/>
+      </c>
+      <c r="J56" s="47">
+        <f>D56-F56-H56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="240" customHeight="1">
+      <c r="A58" s="38" t="inlineStr">
+        <is>
+          <t>※ 입력값: D=출고가, F=공시지원금, G=번이 현금가, H=기변 현금가 (모두 만원 · 음수 허용)
+※ 자동 계산 (봉이지원금 = 할부 시 페이백 금액 · 역산):
+   · I (번이) = D − F − G
+   · J (기변) = D − F − H
+※ 봉이 거래 공식 (공시 케이스 — F 사용):
+   · 현금: 출고가 − 공시지원금 − 봉이지원금 = 현금가
+   · 할부: 위 봉이지원금 = 할부 페이백 (개통 14일 후 별도 현금 지급)
+   · 예①) 180 − 50 − 봉이지원금 = 10  → 봉이지원금 = 120만
+   · 예②) 180 − 50 − 봉이지원금 = −10 → 봉이지원금 = 140만 (현금가 음수 = 매장이 고객에 페이백 → 봉이가 매장에 더 보상)
+※ 봉이 거래 공식 (선택약정 25% 케이스 — F 미사용):
+   · 현금: 출고가 − 봉이지원금 = 선약 현금가 (공시지원금 없음)
+   · 할부: 위 봉이지원금 = 선약 할부 페이백
+   · 예) 180 − 봉이지원금 = 30 → 봉이지원금 = 150만 / + 월 요금 25%↓ 별도
+   · 선약 봉이지원금 계산은 F열을 0으로 두고 동일 컬럼(I·J) 사용하거나 별도 행으로 입력
+※ 할부 24개월 / 수수료 5.9% 원리금균등 (할부원금은 통신사 시스템 정책)
+※ 공시지원금 ↔ 선택약정 동시 적용 불가 (택1)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -1292,18 +1292,14 @@
       <c r="F3" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G3" s="46" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H3" s="46" t="n">
-        <v>5</v>
-      </c>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
       <c r="I3" s="47">
-        <f>D3-F3-G3</f>
+        <f>IFERROR(D3-F3-G3,"")</f>
         <v/>
       </c>
       <c r="J3" s="47">
-        <f>D3-F3-H3</f>
+        <f>IFERROR(D3-F3-H3,"")</f>
         <v/>
       </c>
     </row>
@@ -1334,18 +1330,14 @@
       <c r="F4" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G4" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" s="46" t="n">
-        <v>34</v>
-      </c>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
       <c r="I4" s="47">
-        <f>D4-F4-G4</f>
+        <f>IFERROR(D4-F4-G4,"")</f>
         <v/>
       </c>
       <c r="J4" s="47">
-        <f>D4-F4-H4</f>
+        <f>IFERROR(D4-F4-H4,"")</f>
         <v/>
       </c>
     </row>
@@ -1376,18 +1368,14 @@
       <c r="F5" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G5" s="46" t="n">
-        <v>44</v>
-      </c>
-      <c r="H5" s="46" t="n">
-        <v>64</v>
-      </c>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
       <c r="I5" s="47">
-        <f>D5-F5-G5</f>
+        <f>IFERROR(D5-F5-G5,"")</f>
         <v/>
       </c>
       <c r="J5" s="47">
-        <f>D5-F5-H5</f>
+        <f>IFERROR(D5-F5-H5,"")</f>
         <v/>
       </c>
     </row>
@@ -1418,18 +1406,14 @@
       <c r="F6" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G6" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="H6" s="46" t="n">
-        <v>44</v>
-      </c>
+      <c r="G6" s="46" t="n"/>
+      <c r="H6" s="46" t="n"/>
       <c r="I6" s="47">
-        <f>D6-F6-G6</f>
+        <f>IFERROR(D6-F6-G6,"")</f>
         <v/>
       </c>
       <c r="J6" s="47">
-        <f>D6-F6-H6</f>
+        <f>IFERROR(D6-F6-H6,"")</f>
         <v/>
       </c>
     </row>
@@ -1460,18 +1444,14 @@
       <c r="F7" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G7" s="46" t="n">
-        <v>127</v>
-      </c>
-      <c r="H7" s="46" t="n">
-        <v>139</v>
-      </c>
+      <c r="G7" s="46" t="n"/>
+      <c r="H7" s="46" t="n"/>
       <c r="I7" s="47">
-        <f>D7-F7-G7</f>
+        <f>IFERROR(D7-F7-G7,"")</f>
         <v/>
       </c>
       <c r="J7" s="47">
-        <f>D7-F7-H7</f>
+        <f>IFERROR(D7-F7-H7,"")</f>
         <v/>
       </c>
     </row>
@@ -1502,18 +1482,14 @@
       <c r="F8" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="46" t="n">
-        <v>59</v>
-      </c>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="46" t="n"/>
       <c r="I8" s="47">
-        <f>D8-F8-G8</f>
+        <f>IFERROR(D8-F8-G8,"")</f>
         <v/>
       </c>
       <c r="J8" s="47">
-        <f>D8-F8-H8</f>
+        <f>IFERROR(D8-F8-H8,"")</f>
         <v/>
       </c>
     </row>
@@ -1544,18 +1520,14 @@
       <c r="F9" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G9" s="46" t="n">
-        <v>25</v>
-      </c>
-      <c r="H9" s="46" t="n">
-        <v>79</v>
-      </c>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
       <c r="I9" s="47">
-        <f>D9-F9-G9</f>
+        <f>IFERROR(D9-F9-G9,"")</f>
         <v/>
       </c>
       <c r="J9" s="47">
-        <f>D9-F9-H9</f>
+        <f>IFERROR(D9-F9-H9,"")</f>
         <v/>
       </c>
     </row>
@@ -1586,18 +1558,14 @@
       <c r="F10" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G10" s="46" t="n">
-        <v>59</v>
-      </c>
-      <c r="H10" s="46" t="n">
-        <v>114</v>
-      </c>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
       <c r="I10" s="47">
-        <f>D10-F10-G10</f>
+        <f>IFERROR(D10-F10-G10,"")</f>
         <v/>
       </c>
       <c r="J10" s="47">
-        <f>D10-F10-H10</f>
+        <f>IFERROR(D10-F10-H10,"")</f>
         <v/>
       </c>
     </row>
@@ -1628,18 +1596,14 @@
       <c r="F11" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G11" s="46" t="n">
-        <v>39</v>
-      </c>
-      <c r="H11" s="46" t="n">
-        <v>37</v>
-      </c>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="46" t="n"/>
       <c r="I11" s="47">
-        <f>D11-F11-G11</f>
+        <f>IFERROR(D11-F11-G11,"")</f>
         <v/>
       </c>
       <c r="J11" s="47">
-        <f>D11-F11-H11</f>
+        <f>IFERROR(D11-F11-H11,"")</f>
         <v/>
       </c>
     </row>
@@ -1670,18 +1634,14 @@
       <c r="F12" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G12" s="46" t="n">
-        <v>-35</v>
-      </c>
-      <c r="H12" s="46" t="n">
-        <v>-5</v>
-      </c>
+      <c r="G12" s="46" t="n"/>
+      <c r="H12" s="46" t="n"/>
       <c r="I12" s="47">
-        <f>D12-F12-G12</f>
+        <f>IFERROR(D12-F12-G12,"")</f>
         <v/>
       </c>
       <c r="J12" s="47">
-        <f>D12-F12-H12</f>
+        <f>IFERROR(D12-F12-H12,"")</f>
         <v/>
       </c>
     </row>
@@ -1712,18 +1672,14 @@
       <c r="F13" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G13" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="H13" s="46" t="n">
-        <v>59</v>
-      </c>
+      <c r="G13" s="46" t="n"/>
+      <c r="H13" s="46" t="n"/>
       <c r="I13" s="47">
-        <f>D13-F13-G13</f>
+        <f>IFERROR(D13-F13-G13,"")</f>
         <v/>
       </c>
       <c r="J13" s="47">
-        <f>D13-F13-H13</f>
+        <f>IFERROR(D13-F13-H13,"")</f>
         <v/>
       </c>
     </row>
@@ -1754,18 +1710,14 @@
       <c r="F14" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G14" s="46" t="n">
-        <v>74</v>
-      </c>
-      <c r="H14" s="46" t="n">
-        <v>79</v>
-      </c>
+      <c r="G14" s="46" t="n"/>
+      <c r="H14" s="46" t="n"/>
       <c r="I14" s="47">
-        <f>D14-F14-G14</f>
+        <f>IFERROR(D14-F14-G14,"")</f>
         <v/>
       </c>
       <c r="J14" s="47">
-        <f>D14-F14-H14</f>
+        <f>IFERROR(D14-F14-H14,"")</f>
         <v/>
       </c>
     </row>
@@ -1796,18 +1748,14 @@
       <c r="F15" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G15" s="46" t="n">
-        <v>49</v>
-      </c>
-      <c r="H15" s="46" t="n">
-        <v>79</v>
-      </c>
+      <c r="G15" s="46" t="n"/>
+      <c r="H15" s="46" t="n"/>
       <c r="I15" s="47">
-        <f>D15-F15-G15</f>
+        <f>IFERROR(D15-F15-G15,"")</f>
         <v/>
       </c>
       <c r="J15" s="47">
-        <f>D15-F15-H15</f>
+        <f>IFERROR(D15-F15-H15,"")</f>
         <v/>
       </c>
     </row>
@@ -1838,18 +1786,14 @@
       <c r="F16" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G16" s="46" t="n">
-        <v>124</v>
-      </c>
-      <c r="H16" s="46" t="n">
-        <v>129</v>
-      </c>
+      <c r="G16" s="46" t="n"/>
+      <c r="H16" s="46" t="n"/>
       <c r="I16" s="47">
-        <f>D16-F16-G16</f>
+        <f>IFERROR(D16-F16-G16,"")</f>
         <v/>
       </c>
       <c r="J16" s="47">
-        <f>D16-F16-H16</f>
+        <f>IFERROR(D16-F16-H16,"")</f>
         <v/>
       </c>
     </row>
@@ -1880,18 +1824,14 @@
       <c r="F17" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G17" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" s="46" t="n">
-        <v>54</v>
-      </c>
+      <c r="G17" s="46" t="n"/>
+      <c r="H17" s="46" t="n"/>
       <c r="I17" s="47">
-        <f>D17-F17-G17</f>
+        <f>IFERROR(D17-F17-G17,"")</f>
         <v/>
       </c>
       <c r="J17" s="47">
-        <f>D17-F17-H17</f>
+        <f>IFERROR(D17-F17-H17,"")</f>
         <v/>
       </c>
     </row>
@@ -1922,18 +1862,14 @@
       <c r="F18" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G18" s="46" t="n">
-        <v>49</v>
-      </c>
-      <c r="H18" s="46" t="n">
-        <v>84</v>
-      </c>
+      <c r="G18" s="46" t="n"/>
+      <c r="H18" s="46" t="n"/>
       <c r="I18" s="47">
-        <f>D18-F18-G18</f>
+        <f>IFERROR(D18-F18-G18,"")</f>
         <v/>
       </c>
       <c r="J18" s="47">
-        <f>D18-F18-H18</f>
+        <f>IFERROR(D18-F18-H18,"")</f>
         <v/>
       </c>
     </row>
@@ -1964,18 +1900,14 @@
       <c r="F19" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G19" s="46" t="n">
-        <v>59</v>
-      </c>
-      <c r="H19" s="46" t="n">
-        <v>104</v>
-      </c>
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n"/>
       <c r="I19" s="47">
-        <f>D19-F19-G19</f>
+        <f>IFERROR(D19-F19-G19,"")</f>
         <v/>
       </c>
       <c r="J19" s="47">
-        <f>D19-F19-H19</f>
+        <f>IFERROR(D19-F19-H19,"")</f>
         <v/>
       </c>
     </row>
@@ -2006,18 +1938,14 @@
       <c r="F20" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="G20" s="46" t="n">
-        <v>109</v>
-      </c>
-      <c r="H20" s="46" t="n">
-        <v>144</v>
-      </c>
+      <c r="G20" s="46" t="n"/>
+      <c r="H20" s="46" t="n"/>
       <c r="I20" s="47">
-        <f>D20-F20-G20</f>
+        <f>IFERROR(D20-F20-G20,"")</f>
         <v/>
       </c>
       <c r="J20" s="47">
-        <f>D20-F20-H20</f>
+        <f>IFERROR(D20-F20-H20,"")</f>
         <v/>
       </c>
     </row>
@@ -2048,18 +1976,14 @@
       <c r="F21" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G21" s="46" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H21" s="46" t="n">
-        <v>-15</v>
-      </c>
+      <c r="G21" s="46" t="n"/>
+      <c r="H21" s="46" t="n"/>
       <c r="I21" s="47">
-        <f>D21-F21-G21</f>
+        <f>IFERROR(D21-F21-G21,"")</f>
         <v/>
       </c>
       <c r="J21" s="47">
-        <f>D21-F21-H21</f>
+        <f>IFERROR(D21-F21-H21,"")</f>
         <v/>
       </c>
     </row>
@@ -2090,18 +2014,14 @@
       <c r="F22" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G22" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="46" t="n">
-        <v>5</v>
-      </c>
+      <c r="G22" s="46" t="n"/>
+      <c r="H22" s="46" t="n"/>
       <c r="I22" s="47">
-        <f>D22-F22-G22</f>
+        <f>IFERROR(D22-F22-G22,"")</f>
         <v/>
       </c>
       <c r="J22" s="47">
-        <f>D22-F22-H22</f>
+        <f>IFERROR(D22-F22-H22,"")</f>
         <v/>
       </c>
     </row>
@@ -2132,18 +2052,14 @@
       <c r="F23" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G23" s="46" t="n">
-        <v>34</v>
-      </c>
-      <c r="H23" s="46" t="n">
-        <v>39</v>
-      </c>
+      <c r="G23" s="46" t="n"/>
+      <c r="H23" s="46" t="n"/>
       <c r="I23" s="47">
-        <f>D23-F23-G23</f>
+        <f>IFERROR(D23-F23-G23,"")</f>
         <v/>
       </c>
       <c r="J23" s="47">
-        <f>D23-F23-H23</f>
+        <f>IFERROR(D23-F23-H23,"")</f>
         <v/>
       </c>
     </row>
@@ -2174,18 +2090,14 @@
       <c r="F24" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G24" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="46" t="n">
-        <v>5</v>
-      </c>
+      <c r="G24" s="46" t="n"/>
+      <c r="H24" s="46" t="n"/>
       <c r="I24" s="47">
-        <f>D24-F24-G24</f>
+        <f>IFERROR(D24-F24-G24,"")</f>
         <v/>
       </c>
       <c r="J24" s="47">
-        <f>D24-F24-H24</f>
+        <f>IFERROR(D24-F24-H24,"")</f>
         <v/>
       </c>
     </row>
@@ -2216,18 +2128,14 @@
       <c r="F25" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="46" t="n">
-        <v>99</v>
-      </c>
-      <c r="H25" s="46" t="n">
-        <v>104</v>
-      </c>
+      <c r="G25" s="46" t="n"/>
+      <c r="H25" s="46" t="n"/>
       <c r="I25" s="47">
-        <f>D25-F25-G25</f>
+        <f>IFERROR(D25-F25-G25,"")</f>
         <v/>
       </c>
       <c r="J25" s="47">
-        <f>D25-F25-H25</f>
+        <f>IFERROR(D25-F25-H25,"")</f>
         <v/>
       </c>
     </row>
@@ -2258,18 +2166,14 @@
       <c r="F26" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G26" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="46" t="n">
-        <v>19</v>
-      </c>
+      <c r="G26" s="46" t="n"/>
+      <c r="H26" s="46" t="n"/>
       <c r="I26" s="47">
-        <f>D26-F26-G26</f>
+        <f>IFERROR(D26-F26-G26,"")</f>
         <v/>
       </c>
       <c r="J26" s="47">
-        <f>D26-F26-H26</f>
+        <f>IFERROR(D26-F26-H26,"")</f>
         <v/>
       </c>
     </row>
@@ -2300,18 +2204,14 @@
       <c r="F27" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G27" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="H27" s="46" t="n">
-        <v>39</v>
-      </c>
+      <c r="G27" s="46" t="n"/>
+      <c r="H27" s="46" t="n"/>
       <c r="I27" s="47">
-        <f>D27-F27-G27</f>
+        <f>IFERROR(D27-F27-G27,"")</f>
         <v/>
       </c>
       <c r="J27" s="47">
-        <f>D27-F27-H27</f>
+        <f>IFERROR(D27-F27-H27,"")</f>
         <v/>
       </c>
     </row>
@@ -2342,18 +2242,14 @@
       <c r="F28" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="46" t="n">
-        <v>54</v>
-      </c>
-      <c r="H28" s="46" t="n">
-        <v>74</v>
-      </c>
+      <c r="G28" s="46" t="n"/>
+      <c r="H28" s="46" t="n"/>
       <c r="I28" s="47">
-        <f>D28-F28-G28</f>
+        <f>IFERROR(D28-F28-G28,"")</f>
         <v/>
       </c>
       <c r="J28" s="47">
-        <f>D28-F28-H28</f>
+        <f>IFERROR(D28-F28-H28,"")</f>
         <v/>
       </c>
     </row>
@@ -2384,18 +2280,14 @@
       <c r="F29" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="46" t="n">
-        <v>0</v>
-      </c>
+      <c r="G29" s="46" t="n"/>
+      <c r="H29" s="46" t="n"/>
       <c r="I29" s="47">
-        <f>D29-F29-G29</f>
+        <f>IFERROR(D29-F29-G29,"")</f>
         <v/>
       </c>
       <c r="J29" s="47">
-        <f>D29-F29-H29</f>
+        <f>IFERROR(D29-F29-H29,"")</f>
         <v/>
       </c>
     </row>
@@ -2426,18 +2318,14 @@
       <c r="F30" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G30" s="46" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H30" s="46" t="n">
-        <v>-25</v>
-      </c>
+      <c r="G30" s="46" t="n"/>
+      <c r="H30" s="46" t="n"/>
       <c r="I30" s="47">
-        <f>D30-F30-G30</f>
+        <f>IFERROR(D30-F30-G30,"")</f>
         <v/>
       </c>
       <c r="J30" s="47">
-        <f>D30-F30-H30</f>
+        <f>IFERROR(D30-F30-H30,"")</f>
         <v/>
       </c>
     </row>
@@ -2468,18 +2356,14 @@
       <c r="F31" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G31" s="46" t="n">
-        <v>-55</v>
-      </c>
-      <c r="H31" s="46" t="n">
-        <v>-30</v>
-      </c>
+      <c r="G31" s="46" t="n"/>
+      <c r="H31" s="46" t="n"/>
       <c r="I31" s="47">
-        <f>D31-F31-G31</f>
+        <f>IFERROR(D31-F31-G31,"")</f>
         <v/>
       </c>
       <c r="J31" s="47">
-        <f>D31-F31-H31</f>
+        <f>IFERROR(D31-F31-H31,"")</f>
         <v/>
       </c>
     </row>
@@ -2510,18 +2394,14 @@
       <c r="F32" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G32" s="46" t="n">
-        <v>-45</v>
-      </c>
-      <c r="H32" s="46" t="n">
-        <v>-20</v>
-      </c>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="46" t="n"/>
       <c r="I32" s="47">
-        <f>D32-F32-G32</f>
+        <f>IFERROR(D32-F32-G32,"")</f>
         <v/>
       </c>
       <c r="J32" s="47">
-        <f>D32-F32-H32</f>
+        <f>IFERROR(D32-F32-H32,"")</f>
         <v/>
       </c>
     </row>
@@ -2552,18 +2432,14 @@
       <c r="F33" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G33" s="46" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H33" s="46" t="n">
-        <v>0</v>
-      </c>
+      <c r="G33" s="46" t="n"/>
+      <c r="H33" s="46" t="n"/>
       <c r="I33" s="47">
-        <f>D33-F33-G33</f>
+        <f>IFERROR(D33-F33-G33,"")</f>
         <v/>
       </c>
       <c r="J33" s="47">
-        <f>D33-F33-H33</f>
+        <f>IFERROR(D33-F33-H33,"")</f>
         <v/>
       </c>
     </row>
@@ -2594,18 +2470,14 @@
       <c r="F34" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G34" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="H34" s="46" t="n">
-        <v>34</v>
-      </c>
+      <c r="G34" s="46" t="n"/>
+      <c r="H34" s="46" t="n"/>
       <c r="I34" s="47">
-        <f>D34-F34-G34</f>
+        <f>IFERROR(D34-F34-G34,"")</f>
         <v/>
       </c>
       <c r="J34" s="47">
-        <f>D34-F34-H34</f>
+        <f>IFERROR(D34-F34-H34,"")</f>
         <v/>
       </c>
     </row>
@@ -2636,18 +2508,14 @@
       <c r="F35" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G35" s="46" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H35" s="46" t="n">
-        <v>24</v>
-      </c>
+      <c r="G35" s="46" t="n"/>
+      <c r="H35" s="46" t="n"/>
       <c r="I35" s="47">
-        <f>D35-F35-G35</f>
+        <f>IFERROR(D35-F35-G35,"")</f>
         <v/>
       </c>
       <c r="J35" s="47">
-        <f>D35-F35-H35</f>
+        <f>IFERROR(D35-F35-H35,"")</f>
         <v/>
       </c>
     </row>
@@ -2678,18 +2546,14 @@
       <c r="F36" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G36" s="46" t="n">
-        <v>34</v>
-      </c>
-      <c r="H36" s="46" t="n">
-        <v>54</v>
-      </c>
+      <c r="G36" s="46" t="n"/>
+      <c r="H36" s="46" t="n"/>
       <c r="I36" s="47">
-        <f>D36-F36-G36</f>
+        <f>IFERROR(D36-F36-G36,"")</f>
         <v/>
       </c>
       <c r="J36" s="47">
-        <f>D36-F36-H36</f>
+        <f>IFERROR(D36-F36-H36,"")</f>
         <v/>
       </c>
     </row>
@@ -2720,18 +2584,14 @@
       <c r="F37" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G37" s="46" t="n">
-        <v>59</v>
-      </c>
-      <c r="H37" s="46" t="n">
-        <v>79</v>
-      </c>
+      <c r="G37" s="46" t="n"/>
+      <c r="H37" s="46" t="n"/>
       <c r="I37" s="47">
-        <f>D37-F37-G37</f>
+        <f>IFERROR(D37-F37-G37,"")</f>
         <v/>
       </c>
       <c r="J37" s="47">
-        <f>D37-F37-H37</f>
+        <f>IFERROR(D37-F37-H37,"")</f>
         <v/>
       </c>
     </row>
@@ -2762,18 +2622,14 @@
       <c r="F38" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="G38" s="46" t="n">
-        <v>94</v>
-      </c>
-      <c r="H38" s="46" t="n">
-        <v>124</v>
-      </c>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
       <c r="I38" s="47">
-        <f>D38-F38-G38</f>
+        <f>IFERROR(D38-F38-G38,"")</f>
         <v/>
       </c>
       <c r="J38" s="47">
-        <f>D38-F38-H38</f>
+        <f>IFERROR(D38-F38-H38,"")</f>
         <v/>
       </c>
     </row>
@@ -2804,18 +2660,14 @@
       <c r="F39" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G39" s="46" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H39" s="46" t="n">
-        <v>-20</v>
-      </c>
+      <c r="G39" s="46" t="n"/>
+      <c r="H39" s="46" t="n"/>
       <c r="I39" s="47">
-        <f>D39-F39-G39</f>
+        <f>IFERROR(D39-F39-G39,"")</f>
         <v/>
       </c>
       <c r="J39" s="47">
-        <f>D39-F39-H39</f>
+        <f>IFERROR(D39-F39-H39,"")</f>
         <v/>
       </c>
     </row>
@@ -2846,18 +2698,14 @@
       <c r="F40" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G40" s="46" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H40" s="46" t="n">
-        <v>0</v>
-      </c>
+      <c r="G40" s="46" t="n"/>
+      <c r="H40" s="46" t="n"/>
       <c r="I40" s="47">
-        <f>D40-F40-G40</f>
+        <f>IFERROR(D40-F40-G40,"")</f>
         <v/>
       </c>
       <c r="J40" s="47">
-        <f>D40-F40-H40</f>
+        <f>IFERROR(D40-F40-H40,"")</f>
         <v/>
       </c>
     </row>
@@ -2888,18 +2736,14 @@
       <c r="F41" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G41" s="46" t="n">
-        <v>29</v>
-      </c>
-      <c r="H41" s="46" t="n">
-        <v>34</v>
-      </c>
+      <c r="G41" s="46" t="n"/>
+      <c r="H41" s="46" t="n"/>
       <c r="I41" s="47">
-        <f>D41-F41-G41</f>
+        <f>IFERROR(D41-F41-G41,"")</f>
         <v/>
       </c>
       <c r="J41" s="47">
-        <f>D41-F41-H41</f>
+        <f>IFERROR(D41-F41-H41,"")</f>
         <v/>
       </c>
     </row>
@@ -2930,18 +2774,14 @@
       <c r="F42" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G42" s="46" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H42" s="46" t="n">
-        <v>-5</v>
-      </c>
+      <c r="G42" s="46" t="n"/>
+      <c r="H42" s="46" t="n"/>
       <c r="I42" s="47">
-        <f>D42-F42-G42</f>
+        <f>IFERROR(D42-F42-G42,"")</f>
         <v/>
       </c>
       <c r="J42" s="47">
-        <f>D42-F42-H42</f>
+        <f>IFERROR(D42-F42-H42,"")</f>
         <v/>
       </c>
     </row>
@@ -2972,18 +2812,14 @@
       <c r="F43" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G43" s="46" t="n">
-        <v>94</v>
-      </c>
-      <c r="H43" s="46" t="n">
-        <v>94</v>
-      </c>
+      <c r="G43" s="46" t="n"/>
+      <c r="H43" s="46" t="n"/>
       <c r="I43" s="47">
-        <f>D43-F43-G43</f>
+        <f>IFERROR(D43-F43-G43,"")</f>
         <v/>
       </c>
       <c r="J43" s="47">
-        <f>D43-F43-H43</f>
+        <f>IFERROR(D43-F43-H43,"")</f>
         <v/>
       </c>
     </row>
@@ -3014,18 +2850,14 @@
       <c r="F44" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G44" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="H44" s="46" t="n">
-        <v>24</v>
-      </c>
+      <c r="G44" s="46" t="n"/>
+      <c r="H44" s="46" t="n"/>
       <c r="I44" s="47">
-        <f>D44-F44-G44</f>
+        <f>IFERROR(D44-F44-G44,"")</f>
         <v/>
       </c>
       <c r="J44" s="47">
-        <f>D44-F44-H44</f>
+        <f>IFERROR(D44-F44-H44,"")</f>
         <v/>
       </c>
     </row>
@@ -3056,18 +2888,14 @@
       <c r="F45" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G45" s="46" t="n">
-        <v>39</v>
-      </c>
-      <c r="H45" s="46" t="n">
-        <v>44</v>
-      </c>
+      <c r="G45" s="46" t="n"/>
+      <c r="H45" s="46" t="n"/>
       <c r="I45" s="47">
-        <f>D45-F45-G45</f>
+        <f>IFERROR(D45-F45-G45,"")</f>
         <v/>
       </c>
       <c r="J45" s="47">
-        <f>D45-F45-H45</f>
+        <f>IFERROR(D45-F45-H45,"")</f>
         <v/>
       </c>
     </row>
@@ -3098,18 +2926,14 @@
       <c r="F46" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G46" s="46" t="n">
-        <v>74</v>
-      </c>
-      <c r="H46" s="46" t="n">
-        <v>78</v>
-      </c>
+      <c r="G46" s="46" t="n"/>
+      <c r="H46" s="46" t="n"/>
       <c r="I46" s="47">
-        <f>D46-F46-G46</f>
+        <f>IFERROR(D46-F46-G46,"")</f>
         <v/>
       </c>
       <c r="J46" s="47">
-        <f>D46-F46-H46</f>
+        <f>IFERROR(D46-F46-H46,"")</f>
         <v/>
       </c>
     </row>
@@ -3140,18 +2964,14 @@
       <c r="F47" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G47" s="46" t="n">
-        <v>-20</v>
-      </c>
-      <c r="H47" s="46" t="n">
-        <v>5</v>
-      </c>
+      <c r="G47" s="46" t="n"/>
+      <c r="H47" s="46" t="n"/>
       <c r="I47" s="47">
-        <f>D47-F47-G47</f>
+        <f>IFERROR(D47-F47-G47,"")</f>
         <v/>
       </c>
       <c r="J47" s="47">
-        <f>D47-F47-H47</f>
+        <f>IFERROR(D47-F47-H47,"")</f>
         <v/>
       </c>
     </row>
@@ -3182,18 +3002,14 @@
       <c r="F48" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G48" s="46" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H48" s="46" t="n">
-        <v>-15</v>
-      </c>
+      <c r="G48" s="46" t="n"/>
+      <c r="H48" s="46" t="n"/>
       <c r="I48" s="47">
-        <f>D48-F48-G48</f>
+        <f>IFERROR(D48-F48-G48,"")</f>
         <v/>
       </c>
       <c r="J48" s="47">
-        <f>D48-F48-H48</f>
+        <f>IFERROR(D48-F48-H48,"")</f>
         <v/>
       </c>
     </row>
@@ -3224,18 +3040,14 @@
       <c r="F49" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G49" s="46" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H49" s="46" t="n">
-        <v>14</v>
-      </c>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="46" t="n"/>
       <c r="I49" s="47">
-        <f>D49-F49-G49</f>
+        <f>IFERROR(D49-F49-G49,"")</f>
         <v/>
       </c>
       <c r="J49" s="47">
-        <f>D49-F49-H49</f>
+        <f>IFERROR(D49-F49-H49,"")</f>
         <v/>
       </c>
     </row>
@@ -3266,18 +3078,14 @@
       <c r="F50" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G50" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="46" t="n">
-        <v>54</v>
-      </c>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="46" t="n"/>
       <c r="I50" s="47">
-        <f>D50-F50-G50</f>
+        <f>IFERROR(D50-F50-G50,"")</f>
         <v/>
       </c>
       <c r="J50" s="47">
-        <f>D50-F50-H50</f>
+        <f>IFERROR(D50-F50-H50,"")</f>
         <v/>
       </c>
     </row>
@@ -3308,18 +3116,14 @@
       <c r="F51" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G51" s="46" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H51" s="46" t="n">
-        <v>44</v>
-      </c>
+      <c r="G51" s="46" t="n"/>
+      <c r="H51" s="46" t="n"/>
       <c r="I51" s="47">
-        <f>D51-F51-G51</f>
+        <f>IFERROR(D51-F51-G51,"")</f>
         <v/>
       </c>
       <c r="J51" s="47">
-        <f>D51-F51-H51</f>
+        <f>IFERROR(D51-F51-H51,"")</f>
         <v/>
       </c>
     </row>
@@ -3350,18 +3154,14 @@
       <c r="F52" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G52" s="46" t="n">
-        <v>29</v>
-      </c>
-      <c r="H52" s="46" t="n">
-        <v>84</v>
-      </c>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="46" t="n"/>
       <c r="I52" s="47">
-        <f>D52-F52-G52</f>
+        <f>IFERROR(D52-F52-G52,"")</f>
         <v/>
       </c>
       <c r="J52" s="47">
-        <f>D52-F52-H52</f>
+        <f>IFERROR(D52-F52-H52,"")</f>
         <v/>
       </c>
     </row>
@@ -3392,18 +3192,14 @@
       <c r="F53" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G53" s="46" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H53" s="46" t="n">
-        <v>19</v>
-      </c>
+      <c r="G53" s="46" t="n"/>
+      <c r="H53" s="46" t="n"/>
       <c r="I53" s="47">
-        <f>D53-F53-G53</f>
+        <f>IFERROR(D53-F53-G53,"")</f>
         <v/>
       </c>
       <c r="J53" s="47">
-        <f>D53-F53-H53</f>
+        <f>IFERROR(D53-F53-H53,"")</f>
         <v/>
       </c>
     </row>
@@ -3434,18 +3230,14 @@
       <c r="F54" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G54" s="46" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H54" s="46" t="n">
-        <v>49</v>
-      </c>
+      <c r="G54" s="46" t="n"/>
+      <c r="H54" s="46" t="n"/>
       <c r="I54" s="47">
-        <f>D54-F54-G54</f>
+        <f>IFERROR(D54-F54-G54,"")</f>
         <v/>
       </c>
       <c r="J54" s="47">
-        <f>D54-F54-H54</f>
+        <f>IFERROR(D54-F54-H54,"")</f>
         <v/>
       </c>
     </row>
@@ -3476,18 +3268,14 @@
       <c r="F55" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G55" s="46" t="n">
-        <v>34</v>
-      </c>
-      <c r="H55" s="46" t="n">
-        <v>69</v>
-      </c>
+      <c r="G55" s="46" t="n"/>
+      <c r="H55" s="46" t="n"/>
       <c r="I55" s="47">
-        <f>D55-F55-G55</f>
+        <f>IFERROR(D55-F55-G55,"")</f>
         <v/>
       </c>
       <c r="J55" s="47">
-        <f>D55-F55-H55</f>
+        <f>IFERROR(D55-F55-H55,"")</f>
         <v/>
       </c>
     </row>
@@ -3518,25 +3306,24 @@
       <c r="F56" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="G56" s="46" t="n">
-        <v>89</v>
-      </c>
-      <c r="H56" s="46" t="n">
-        <v>114</v>
-      </c>
+      <c r="G56" s="46" t="n"/>
+      <c r="H56" s="46" t="n"/>
       <c r="I56" s="47">
-        <f>D56-F56-G56</f>
+        <f>IFERROR(D56-F56-G56,"")</f>
         <v/>
       </c>
       <c r="J56" s="47">
-        <f>D56-F56-H56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="240" customHeight="1">
+        <f>IFERROR(D56-F56-H56,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58" ht="260" customHeight="1">
       <c r="A58" s="38" t="inlineStr">
         <is>
-          <t>※ 입력값: D=출고가, F=공시지원금, G=번이 현금가, H=기변 현금가 (모두 만원 · 음수 허용)
+          <t>※ G(번이 현금가) · H(기변 현금가)는 빈칸 — 매장이 직접 입력
+※ I·J 봉이지원금은 G·H 입력 시 자동 계산 (빈 행은 빈칸 표시)
+※ 입력값: D=출고가, F=공시지원금, G=번이 현금가, H=기변 현금가 (모두 만원 · 음수 허용)
 ※ 자동 계산 (봉이지원금 = 할부 시 페이백 금액 · 역산):
    · I (번이) = D − F − G
    · J (기변) = D − F − H

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -4,9 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
-    <sheet name="무선_휴대폰" sheetId="2" r:id="rId2"/>
-    <sheet name="유심_정책" sheetId="3" r:id="rId3"/>
-    <sheet name="인터넷TV_사은품" sheetId="4" r:id="rId4"/>
+    <sheet name="① 무선(휴대폰)" sheetId="2" r:id="rId2"/>
+    <sheet name="② 유심" sheetId="3" r:id="rId3"/>
+    <sheet name="③ 인터넷+TV 사은품" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -35,8 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,9 +401,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A28"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,175 +418,188 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>[할부 정책]</v>
+        <v>[변경 사항]</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>- 할부 = (출고가 - 공시지원금 - 매장지원금) / N개월 (24/30/36)</v>
+        <v>- 옛 무선 10컬럼 → 새 8컬럼 (자동계산 I·J 봉이지원금 컬럼 제거)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>- 할부 시 매장지원금이 위약금으로 잡힘 (24개월 유지 의무, 미달 시 잔여 매장지원금 반환)</v>
+        <v>- 입력 항목 그대로 유지: 통신사/펫네임/용량/출고가/요금제/공시/번이 현금가/기변 현금가</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>- 현금 일시불 = 매장지원금 즉시 차감, 위약금 없음</v>
+        <v>- 자동계산 컬럼 폐기 이유: 할부 페이백 개념 없음 (정책 정정)</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>- 현금가 &lt;= 0 (기기값 0원 + 페이백) = 할부 차단, 현금 개통만 가능</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>[할부 정책 (정정)]</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[무선 컬럼 구조 (8개 입력, 자동계산 없음)]</v>
+        <v>1. 할부 = (출고가 - 공시지원금 - 매장지원금) / N개월 (24/30/36)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1. 통신사 (SK/KT/LG)</v>
+        <v>2. 할부 시 매장지원금이 위약금으로 잡힘 (24개월 유지 의무)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2. 펫네임 (예: S26U, S26, iPhone17 등)</v>
+        <v>3. 현금 일시불 = 매장지원금 즉시 차감 / 위약금 없음</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3. 용량 (256GB/512GB/1TB)</v>
+        <v>4. 현금가 &lt;= 0 (기기값 0원 + 페이백) = 할부 차단 / 현금 개통만</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>4. 출고가 (만원)</v>
+        <v>5. 옛 봉이지원금 / 할부 페이백 / 14일 후 별도 지급 개념 폐기</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5. 요금제 (월요금)</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6. 공시지원금 (만원, 통신사·요금제별 차등, 선약 25% 선택 시 0)</v>
+        <v>[운영자 입력 8컬럼]</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>7. 매장지원금_번이 (만원, 직접 입력)</v>
+        <v>1. 통신사 (SK/KT/LG)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>8. 매장지원금_기변 (만원, 직접 입력)</v>
+        <v>2. 펫네임 (예: S26U, S26, iPhone17 등)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>3. 용량 (256GB/512GB/1TB)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>※ 자동계산 컬럼 폐기 - 봉이지원금/할부 페이백 개념 없음</v>
+        <v>4. 출고가 (만원)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>※ 현금가는 시스템 자동 표시 (출고가 - 공시 - 매장지원금)</v>
+        <v>5. 요금제 (월요금)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>※ 음수 매장지원금 허용 (예: 유심에서 -40 = 고객 수령 40,000원)</v>
+        <v>6. 공시지원금 (만원, 통신사/요금제별 차등, 선약 25% 선택 시 0)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>※ Upsert PK: (통신사 + 펫네임 + 용량 + 요금제) - 동일 조합 업로드 시 덮어쓰기</v>
+        <v>7. 번이 현금가 (만원, 입력)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>8. 기변 현금가 (만원, 입력)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>※ 매장지원금은 시스템 내부에서 자동 계산 (출고가 - 공시 - 현금가) - 화면 표시는 어드민에서</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>※ Upsert PK 무선: (통신사 + 펫네임 + 용량 + 요금제)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>※ Upsert PK 유심: (통신사 + 요금제)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>※ Upsert PK 사은품: (통신사 + 구분 + 상품 구성)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H58"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>무선(휴대폰) 시세 · 입력=현금가 (자동계산 컬럼 폐기 — 할부 페이백 개념 없음)</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
         <v>통신사</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B2" t="str">
         <v>펫네임</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C2" t="str">
         <v>용량</v>
       </c>
-      <c r="D1" t="str">
-        <v>출고가(만원)</v>
-      </c>
-      <c r="E1" t="str">
+      <c r="D2" t="str" xml:space="preserve">
+        <v xml:space="preserve">출고가
+(만원)</v>
+      </c>
+      <c r="E2" t="str">
         <v>요금제(월요금)</v>
       </c>
-      <c r="F1" t="str">
-        <v>공시지원금(만원)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>매장지원금_번이(만원)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>매장지원금_기변(만원)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SK</v>
-      </c>
-      <c r="B2" t="str">
-        <v>S26U</v>
-      </c>
-      <c r="C2" t="str">
-        <v>256GB</v>
-      </c>
-      <c r="D2">
-        <v>160</v>
-      </c>
-      <c r="E2" t="str">
-        <v>프리미엄(125,000)</v>
-      </c>
-      <c r="F2">
-        <v>40</v>
-      </c>
-      <c r="G2">
-        <v>80</v>
-      </c>
-      <c r="H2">
-        <v>60</v>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">공시지원금
+(만원)</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">번이 현금가
+(만원·입력)</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">기변 현금가
+(만원·입력)</v>
       </c>
     </row>
     <row r="3">
@@ -593,25 +607,19 @@
         <v>SK</v>
       </c>
       <c r="B3" t="str">
-        <v>S26U</v>
+        <v>S26</v>
       </c>
       <c r="C3" t="str">
         <v>512GB</v>
       </c>
       <c r="D3">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="E3" t="str">
         <v>프리미엄(125,000)</v>
       </c>
       <c r="F3">
         <v>45</v>
-      </c>
-      <c r="G3">
-        <v>91</v>
-      </c>
-      <c r="H3">
-        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -619,226 +627,1117 @@
         <v>SK</v>
       </c>
       <c r="B4" t="str">
-        <v>S26U</v>
+        <v>S26+</v>
       </c>
       <c r="C4" t="str">
-        <v>1TB</v>
+        <v>512GB</v>
       </c>
       <c r="D4">
-        <v>200</v>
+        <v>145</v>
       </c>
       <c r="E4" t="str">
         <v>프리미엄(125,000)</v>
       </c>
       <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>80</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KT</v>
+        <v>SK</v>
       </c>
       <c r="B5" t="str">
         <v>S26U</v>
       </c>
       <c r="C5" t="str">
-        <v>256GB</v>
+        <v>512GB</v>
       </c>
       <c r="D5">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E5" t="str">
-        <v>초이스스페셜(130,000)</v>
+        <v>프리미엄(125,000)</v>
       </c>
       <c r="F5">
         <v>45</v>
       </c>
-      <c r="G5">
-        <v>85</v>
-      </c>
-      <c r="H5">
-        <v>80</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>KT</v>
+        <v>SK</v>
       </c>
       <c r="B6" t="str">
-        <v>S26U</v>
+        <v>플립7</v>
       </c>
       <c r="C6" t="str">
         <v>512GB</v>
       </c>
       <c r="D6">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E6" t="str">
-        <v>초이스스페셜(130,000)</v>
+        <v>프리미엄(125,000)</v>
       </c>
       <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>96</v>
-      </c>
-      <c r="H6">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>KT</v>
+        <v>SK</v>
       </c>
       <c r="B7" t="str">
-        <v>S26U</v>
+        <v>폴드7</v>
       </c>
       <c r="C7" t="str">
-        <v>1TB</v>
+        <v>512GB</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E7" t="str">
-        <v>초이스스페셜(130,000)</v>
+        <v>프리미엄(125,000)</v>
       </c>
       <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>106</v>
-      </c>
-      <c r="H7">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LG</v>
+        <v>SK</v>
       </c>
       <c r="B8" t="str">
-        <v>S26U</v>
+        <v>S25</v>
       </c>
       <c r="C8" t="str">
-        <v>256GB</v>
+        <v>512GB</v>
       </c>
       <c r="D8">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="E8" t="str">
-        <v>프리미어 슈퍼(125,000)</v>
+        <v>프리미엄(125,000)</v>
       </c>
       <c r="F8">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>95</v>
-      </c>
-      <c r="H8">
-        <v>90</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LG</v>
+        <v>SK</v>
       </c>
       <c r="B9" t="str">
-        <v>S26U</v>
+        <v>S25+</v>
       </c>
       <c r="C9" t="str">
         <v>512GB</v>
       </c>
       <c r="D9">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="E9" t="str">
-        <v>프리미어 슈퍼(125,000)</v>
+        <v>프리미엄(125,000)</v>
       </c>
       <c r="F9">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>104</v>
-      </c>
-      <c r="H9">
-        <v>99</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B10" t="str">
+        <v>S25U</v>
+      </c>
+      <c r="C10" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D10">
+        <v>170</v>
+      </c>
+      <c r="E10" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B11" t="str">
+        <v>S25엣지</v>
+      </c>
+      <c r="C11" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D11">
+        <v>150</v>
+      </c>
+      <c r="E11" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B12" t="str">
+        <v>S25 FE</v>
+      </c>
+      <c r="C12" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D12">
+        <v>95</v>
+      </c>
+      <c r="E12" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B13" t="str">
+        <v>아이폰16</v>
+      </c>
+      <c r="C13" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D13">
+        <v>125</v>
+      </c>
+      <c r="E13" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B14" t="str">
+        <v>아이폰16 플러스</v>
+      </c>
+      <c r="C14" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D14">
+        <v>140</v>
+      </c>
+      <c r="E14" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B15" t="str">
+        <v>아이폰16 프로</v>
+      </c>
+      <c r="C15" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D15">
+        <v>155</v>
+      </c>
+      <c r="E15" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B16" t="str">
+        <v>아이폰16 프로맥스 256G</v>
+      </c>
+      <c r="C16" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D16">
+        <v>190</v>
+      </c>
+      <c r="E16" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B17" t="str">
+        <v>아이폰 17</v>
+      </c>
+      <c r="C17" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D17">
+        <v>130</v>
+      </c>
+      <c r="E17" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B18" t="str">
+        <v>아이폰17 AIR</v>
+      </c>
+      <c r="C18" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D18">
+        <v>160</v>
+      </c>
+      <c r="E18" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F18">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B19" t="str">
+        <v>아이폰17 PRO</v>
+      </c>
+      <c r="C19" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D19">
+        <v>175</v>
+      </c>
+      <c r="E19" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F19">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SK</v>
+      </c>
+      <c r="B20" t="str">
+        <v>아이폰17 프로맥스</v>
+      </c>
+      <c r="C20" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D20">
+        <v>200</v>
+      </c>
+      <c r="E20" t="str">
+        <v>프리미엄(125,000)</v>
+      </c>
+      <c r="F20">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B21" t="str">
+        <v>S26</v>
+      </c>
+      <c r="C21" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D21">
+        <v>130</v>
+      </c>
+      <c r="E21" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B22" t="str">
+        <v>S26+</v>
+      </c>
+      <c r="C22" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D22">
+        <v>145</v>
+      </c>
+      <c r="E22" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B23" t="str">
+        <v>S26U</v>
+      </c>
+      <c r="C23" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D23">
+        <v>180</v>
+      </c>
+      <c r="E23" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B24" t="str">
+        <v>플립7</v>
+      </c>
+      <c r="C24" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D24">
+        <v>150</v>
+      </c>
+      <c r="E24" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B25" t="str">
+        <v>폴드7</v>
+      </c>
+      <c r="C25" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D25">
+        <v>230</v>
+      </c>
+      <c r="E25" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B26" t="str">
+        <v>S25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D26">
+        <v>115</v>
+      </c>
+      <c r="E26" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B27" t="str">
+        <v>S25+</v>
+      </c>
+      <c r="C27" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D27">
+        <v>130</v>
+      </c>
+      <c r="E27" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B28" t="str">
+        <v>S25U</v>
+      </c>
+      <c r="C28" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D28">
+        <v>170</v>
+      </c>
+      <c r="E28" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B29" t="str">
+        <v>S25엣지</v>
+      </c>
+      <c r="C29" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D29">
+        <v>150</v>
+      </c>
+      <c r="E29" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B30" t="str">
+        <v>S25 FE</v>
+      </c>
+      <c r="C30" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D30">
+        <v>95</v>
+      </c>
+      <c r="E30" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B31" t="str">
+        <v>아이폰16</v>
+      </c>
+      <c r="C31" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D31">
+        <v>125</v>
+      </c>
+      <c r="E31" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B32" t="str">
+        <v>아이폰16 플러스</v>
+      </c>
+      <c r="C32" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D32">
+        <v>140</v>
+      </c>
+      <c r="E32" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B33" t="str">
+        <v>아이폰16 프로</v>
+      </c>
+      <c r="C33" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D33">
+        <v>155</v>
+      </c>
+      <c r="E33" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B34" t="str">
+        <v>아이폰16 프로맥스 256G</v>
+      </c>
+      <c r="C34" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D34">
+        <v>190</v>
+      </c>
+      <c r="E34" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B35" t="str">
+        <v>아이폰 17</v>
+      </c>
+      <c r="C35" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D35">
+        <v>130</v>
+      </c>
+      <c r="E35" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B36" t="str">
+        <v>아이폰17 AIR</v>
+      </c>
+      <c r="C36" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D36">
+        <v>160</v>
+      </c>
+      <c r="E36" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B37" t="str">
+        <v>아이폰17 PRO</v>
+      </c>
+      <c r="C37" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D37">
+        <v>175</v>
+      </c>
+      <c r="E37" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>KT</v>
+      </c>
+      <c r="B38" t="str">
+        <v>아이폰17 프로맥스</v>
+      </c>
+      <c r="C38" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D38">
+        <v>200</v>
+      </c>
+      <c r="E38" t="str">
+        <v>초이스스페셜(130,000)</v>
+      </c>
+      <c r="F38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>LG</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B39" t="str">
+        <v>S26</v>
+      </c>
+      <c r="C39" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D39">
+        <v>130</v>
+      </c>
+      <c r="E39" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B40" t="str">
+        <v>S26+</v>
+      </c>
+      <c r="C40" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D40">
+        <v>145</v>
+      </c>
+      <c r="E40" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F40">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B41" t="str">
         <v>S26U</v>
       </c>
-      <c r="C10" t="str">
-        <v>1TB</v>
-      </c>
-      <c r="D10">
+      <c r="C41" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D41">
+        <v>180</v>
+      </c>
+      <c r="E41" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F41">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B42" t="str">
+        <v>플립7</v>
+      </c>
+      <c r="C42" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D42">
+        <v>150</v>
+      </c>
+      <c r="E42" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F42">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B43" t="str">
+        <v>폴드7</v>
+      </c>
+      <c r="C43" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D43">
+        <v>230</v>
+      </c>
+      <c r="E43" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F43">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B44" t="str">
+        <v>S25</v>
+      </c>
+      <c r="C44" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D44">
+        <v>115</v>
+      </c>
+      <c r="E44" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F44">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B45" t="str">
+        <v>S25+</v>
+      </c>
+      <c r="C45" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D45">
+        <v>130</v>
+      </c>
+      <c r="E45" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B46" t="str">
+        <v>S25U</v>
+      </c>
+      <c r="C46" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D46">
+        <v>170</v>
+      </c>
+      <c r="E46" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F46">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B47" t="str">
+        <v>S25엣지</v>
+      </c>
+      <c r="C47" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D47">
+        <v>150</v>
+      </c>
+      <c r="E47" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F47">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B48" t="str">
+        <v>S25 FE</v>
+      </c>
+      <c r="C48" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D48">
+        <v>95</v>
+      </c>
+      <c r="E48" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B49" t="str">
+        <v>아이폰16</v>
+      </c>
+      <c r="C49" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D49">
+        <v>125</v>
+      </c>
+      <c r="E49" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B50" t="str">
+        <v>아이폰16 플러스</v>
+      </c>
+      <c r="C50" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D50">
+        <v>140</v>
+      </c>
+      <c r="E50" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F50">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B51" t="str">
+        <v>아이폰16 프로</v>
+      </c>
+      <c r="C51" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D51">
+        <v>155</v>
+      </c>
+      <c r="E51" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F51">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B52" t="str">
+        <v>아이폰16 프로맥스 256G</v>
+      </c>
+      <c r="C52" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D52">
+        <v>190</v>
+      </c>
+      <c r="E52" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F52">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B53" t="str">
+        <v>아이폰 17</v>
+      </c>
+      <c r="C53" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D53">
+        <v>130</v>
+      </c>
+      <c r="E53" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F53">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B54" t="str">
+        <v>아이폰17 AIR</v>
+      </c>
+      <c r="C54" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D54">
+        <v>160</v>
+      </c>
+      <c r="E54" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F54">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B55" t="str">
+        <v>아이폰17 PRO</v>
+      </c>
+      <c r="C55" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D55">
+        <v>175</v>
+      </c>
+      <c r="E55" t="str">
+        <v>프리미어 슈퍼(125,000)</v>
+      </c>
+      <c r="F55">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B56" t="str">
+        <v>아이폰17 프로맥스</v>
+      </c>
+      <c r="C56" t="str">
+        <v>512GB</v>
+      </c>
+      <c r="D56">
         <v>200</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E56" t="str">
         <v>프리미어 슈퍼(125,000)</v>
       </c>
-      <c r="F10">
-        <v>52</v>
-      </c>
-      <c r="G10">
-        <v>113</v>
-      </c>
-      <c r="H10">
-        <v>108</v>
+      <c r="F56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str" xml:space="preserve">
+        <v xml:space="preserve">※ G(번이 현금가) · H(기변 현금가)는 빈칸 — 매장이 직접 입력
+※ I·J 봉이지원금은 G·H 입력 시 자동 계산 (빈 행은 빈칸 표시)
+※ 입력값: D=출고가, F=공시지원금, G=번이 현금가, H=기변 현금가 (모두 만원 · 음수 허용)
+※ 자동 계산 (봉이지원금 = 할부 시 페이백 금액 · 역산):
+   · I (번이) = D − F − G
+   · J (기변) = D − F − H
+※ 봉이 거래 공식 (공시 케이스 — F 사용):
+   · 현금: 출고가 − 공시지원금 − 봉이지원금 = 현금가
+   · 할부: 위 봉이지원금 = 할부 페이백 (개통 14일 후 별도 현금 지급)
+   · 예①) 180 − 50 − 봉이지원금 = 10  → 봉이지원금 = 120만
+   · 예②) 180 − 50 − 봉이지원금 = −10 → 봉이지원금 = 140만 (현금가 음수 = 매장이 고객에 페이백 → 봉이가 매장에 더 보상)
+※ 봉이 거래 공식 (선택약정 25% 케이스 — F 미사용):
+   · 현금: 출고가 − 봉이지원금 = 선약 현금가 (공시지원금 없음)
+   · 할부: 위 봉이지원금 = 선약 할부 페이백
+   · 예) 180 − 봉이지원금 = 30 → 봉이지원금 = 150만 / + 월 요금 25%↓ 별도
+   · 선약 봉이지원금 계산은 F열을 0으로 두고 동일 컬럼(I·J) 사용하거나 별도 행으로 입력
+※ 할부 24개월 / 수수료 5.9% 원리금균등 (할부원금은 통신사 시스템 정책)
+※ 공시지원금 ↔ 선택약정 동시 적용 불가 (택1)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H58"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>통신사</v>
-      </c>
-      <c r="B1" t="str">
-        <v>요금제(월요금)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>25%할인_실납(원)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>번이_매장지원금(만원·음수=고객수령)</v>
+        <v> 유심 시세 · 9행 (샘플 값 포함)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SK</v>
+        <v>통신사</v>
       </c>
       <c r="B2" t="str">
-        <v>세이브(33,000)</v>
-      </c>
-      <c r="C2">
-        <v>24750</v>
-      </c>
-      <c r="D2">
-        <v>-40</v>
+        <v>요금제(월요금)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>25%↓실납</v>
+      </c>
+      <c r="D2" t="str">
+        <v>번이</v>
       </c>
     </row>
     <row r="3">
@@ -846,13 +1745,13 @@
         <v>SK</v>
       </c>
       <c r="B3" t="str">
-        <v>베이직 플러스(45,000)</v>
-      </c>
-      <c r="C3">
-        <v>33750</v>
+        <v>5GX 슬림(33,000)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>24,750</v>
       </c>
       <c r="D3">
-        <v>-20</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="4">
@@ -860,27 +1759,27 @@
         <v>SK</v>
       </c>
       <c r="B4" t="str">
-        <v>5GX 레귤러(55,000)</v>
-      </c>
-      <c r="C4">
-        <v>41250</v>
+        <v>베이직 플러스(45,000)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>33,750</v>
       </c>
       <c r="D4">
-        <v>-10</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KT</v>
+        <v>SK</v>
       </c>
       <c r="B5" t="str">
-        <v>5G 슬림 4GB(45,000)</v>
-      </c>
-      <c r="C5">
-        <v>33750</v>
+        <v>5GX 레귤러(55,000)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>41,250</v>
       </c>
       <c r="D5">
-        <v>-15</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="6">
@@ -888,13 +1787,13 @@
         <v>KT</v>
       </c>
       <c r="B6" t="str">
-        <v>5G 심플(50,000)</v>
-      </c>
-      <c r="C6">
-        <v>37500</v>
+        <v>5G 슬림(37,000)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>27,750</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="7">
@@ -902,27 +1801,27 @@
         <v>KT</v>
       </c>
       <c r="B7" t="str">
-        <v>5G 비디오(69,000)</v>
-      </c>
-      <c r="C7">
-        <v>51750</v>
+        <v>5G 심플(50,000)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>37,500</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LG</v>
+        <v>KT</v>
       </c>
       <c r="B8" t="str">
-        <v>5G 에센셜(55,000)</v>
-      </c>
-      <c r="C8">
-        <v>41250</v>
+        <v>5G 비디오(69,000)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>51,750</v>
       </c>
       <c r="D8">
-        <v>-40</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="9">
@@ -930,13 +1829,13 @@
         <v>LG</v>
       </c>
       <c r="B9" t="str">
-        <v>5G 스탠다드(61,000)</v>
-      </c>
-      <c r="C9">
-        <v>45750</v>
+        <v>5G 슬림+(33,000)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>24,750</v>
       </c>
       <c r="D9">
-        <v>-20</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="10">
@@ -944,197 +1843,1157 @@
         <v>LG</v>
       </c>
       <c r="B10" t="str">
+        <v>5G 스탠다드(61,000)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>45,750</v>
+      </c>
+      <c r="D10">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LG</v>
+      </c>
+      <c r="B11" t="str">
         <v>5G 프리미어 레귤러(85,000)</v>
       </c>
-      <c r="C10">
-        <v>63750</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
+      <c r="C11" t="str">
+        <v>63,750</v>
+      </c>
+      <c r="D11">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str" xml:space="preserve">
+        <v xml:space="preserve">※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이(만원)만 입력
+※ 실납 = 월요금 × 0.75 (선택약정 25% 할인 · SK/KT 개통시 · LG 개통 후 고객센터 신청)
+※ 샘플 값 입력됨 — 매장/온라인이 각자 자기 페이백 값으로 덮어쓰기
+※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E66"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>통신사</v>
-      </c>
-      <c r="B1" t="str">
-        <v>유형</v>
-      </c>
-      <c r="C1" t="str">
-        <v>속도</v>
-      </c>
-      <c r="D1" t="str">
-        <v>결합옵션</v>
-      </c>
-      <c r="E1" t="str">
-        <v>현금사은품(만원)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>비고</v>
+        <v> 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통) · 63개 상품</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SK</v>
+        <v>#</v>
       </c>
       <c r="B2" t="str">
+        <v>통신사</v>
+      </c>
+      <c r="C2" t="str">
+        <v>구분</v>
+      </c>
+      <c r="D2" t="str">
+        <v>상품 구성</v>
+      </c>
+      <c r="E2" t="str">
+        <v>사은품(원)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C3" t="str">
         <v>단독</v>
       </c>
-      <c r="C2" t="str">
-        <v>100M</v>
-      </c>
-      <c r="D2" t="str">
-        <v>없음</v>
-      </c>
-      <c r="E2">
+      <c r="D3" t="str">
+        <v>인터넷 100M</v>
+      </c>
+      <c r="E3">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C4" t="str">
+        <v>단독</v>
+      </c>
+      <c r="D4" t="str">
+        <v>인터넷 500M</v>
+      </c>
+      <c r="E4">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C5" t="str">
+        <v>단독</v>
+      </c>
+      <c r="D5" t="str">
+        <v>인터넷 1G</v>
+      </c>
+      <c r="E5">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C6" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D6" t="str">
+        <v>인터넷 100M + B tv 이코노미</v>
+      </c>
+      <c r="E6">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C7" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D7" t="str">
+        <v>인터넷 100M + B tv 스탠다드</v>
+      </c>
+      <c r="E7">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C8" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D8" t="str">
+        <v>인터넷 100M + B tv 올</v>
+      </c>
+      <c r="E8">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C9" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D9" t="str">
+        <v>인터넷 100M + B tv 스탠다드 플러스</v>
+      </c>
+      <c r="E9">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C10" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D10" t="str">
+        <v>인터넷 100M + B tv 올 플러스</v>
+      </c>
+      <c r="E10">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C11" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D11" t="str">
+        <v>인터넷 100M + B tv 스탠다드 넷플릭스</v>
+      </c>
+      <c r="E11">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C12" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D12" t="str">
+        <v>인터넷 100M + B tv 올 넷플릭스</v>
+      </c>
+      <c r="E12">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C13" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D13" t="str">
+        <v>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E13">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C14" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D14" t="str">
+        <v>인터넷 100M + B tv 올 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E14">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C15" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D15" t="str">
+        <v>인터넷 500M + B tv 이코노미</v>
+      </c>
+      <c r="E15">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C16" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D16" t="str">
+        <v>인터넷 500M + B tv 스탠다드</v>
+      </c>
+      <c r="E16">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C17" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D17" t="str">
+        <v>인터넷 500M + B tv 올</v>
+      </c>
+      <c r="E17">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C18" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D18" t="str">
+        <v>인터넷 500M + B tv 스탠다드 플러스</v>
+      </c>
+      <c r="E18">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C19" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D19" t="str">
+        <v>인터넷 500M + B tv 올 플러스</v>
+      </c>
+      <c r="E19">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C20" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D20" t="str">
+        <v>인터넷 500M + B tv 스탠다드 넷플릭스</v>
+      </c>
+      <c r="E20">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C21" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D21" t="str">
+        <v>인터넷 500M + B tv 올 넷플릭스</v>
+      </c>
+      <c r="E21">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SK</v>
-      </c>
-      <c r="B3" t="str">
+      <c r="B22" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C22" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D22" t="str">
+        <v>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E22">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C23" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D23" t="str">
+        <v>인터넷 500M + B tv 올 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E23">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C24" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D24" t="str">
+        <v>인터넷 1G + B tv 이코노미</v>
+      </c>
+      <c r="E24">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C25" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D25" t="str">
+        <v>인터넷 1G + B tv 스탠다드</v>
+      </c>
+      <c r="E25">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C26" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D26" t="str">
+        <v>인터넷 1G + B tv 올</v>
+      </c>
+      <c r="E26">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C27" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D27" t="str">
+        <v>인터넷 1G + B tv 스탠다드 플러스</v>
+      </c>
+      <c r="E27">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C28" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D28" t="str">
+        <v>인터넷 1G + B tv 올 플러스</v>
+      </c>
+      <c r="E28">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C29" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D29" t="str">
+        <v>인터넷 1G + B tv 스탠다드 넷플릭스</v>
+      </c>
+      <c r="E29">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C30" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D30" t="str">
+        <v>인터넷 1G + B tv 올 넷플릭스</v>
+      </c>
+      <c r="E30">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C31" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D31" t="str">
+        <v>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E31">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SKT</v>
+      </c>
+      <c r="C32" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D32" t="str">
+        <v>인터넷 1G + B tv 올 넷플릭스 프리미엄</v>
+      </c>
+      <c r="E32">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C33" t="str">
         <v>단독</v>
       </c>
-      <c r="C3" t="str">
-        <v>500M</v>
-      </c>
-      <c r="D3" t="str">
-        <v>없음</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SK</v>
-      </c>
-      <c r="B4" t="str">
-        <v>결합</v>
-      </c>
-      <c r="C4" t="str">
-        <v>500M</v>
-      </c>
-      <c r="D4" t="str">
-        <v>지니TV 베이직</v>
-      </c>
-      <c r="E4">
+      <c r="D33" t="str">
+        <v>인터넷 100M</v>
+      </c>
+      <c r="E33">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C34" t="str">
+        <v>단독</v>
+      </c>
+      <c r="D34" t="str">
+        <v>인터넷 500M</v>
+      </c>
+      <c r="E34">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C35" t="str">
+        <v>단독</v>
+      </c>
+      <c r="D35" t="str">
+        <v>인터넷 1G</v>
+      </c>
+      <c r="E35">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C36" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D36" t="str">
+        <v>인터넷 100M + 지니TV 베이직</v>
+      </c>
+      <c r="E36">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C37" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D37" t="str">
+        <v>인터넷 100M + 지니TV 라이트</v>
+      </c>
+      <c r="E37">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C38" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D38" t="str">
+        <v>인터넷 100M + 지니TV 에센스</v>
+      </c>
+      <c r="E38">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C39" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D39" t="str">
+        <v>인터넷 100M + 지니TV 모든G</v>
+      </c>
+      <c r="E39">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C40" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D40" t="str">
+        <v>인터넷 100M + 지니TV 디즈니+모든G</v>
+      </c>
+      <c r="E40">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C41" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D41" t="str">
+        <v>인터넷 500M + 지니TV 베이직</v>
+      </c>
+      <c r="E41">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>KT</v>
-      </c>
-      <c r="B5" t="str">
+      <c r="B42" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C42" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D42" t="str">
+        <v>인터넷 500M + 지니TV 라이트</v>
+      </c>
+      <c r="E42">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C43" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D43" t="str">
+        <v>인터넷 500M + 지니TV 에센스</v>
+      </c>
+      <c r="E43">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C44" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D44" t="str">
+        <v>인터넷 500M + 지니TV 모든G</v>
+      </c>
+      <c r="E44">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C45" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D45" t="str">
+        <v>인터넷 500M + 지니TV 디즈니+모든G</v>
+      </c>
+      <c r="E45">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C46" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D46" t="str">
+        <v>인터넷 1G + 지니TV 베이직</v>
+      </c>
+      <c r="E46">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C47" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D47" t="str">
+        <v>인터넷 1G + 지니TV 라이트</v>
+      </c>
+      <c r="E47">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C48" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D48" t="str">
+        <v>인터넷 1G + 지니TV 에센스</v>
+      </c>
+      <c r="E48">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C49" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D49" t="str">
+        <v>인터넷 1G + 지니TV 모든G</v>
+      </c>
+      <c r="E49">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="str">
+        <v>KT</v>
+      </c>
+      <c r="C50" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D50" t="str">
+        <v>인터넷 1G + 지니TV 디즈니+모든G</v>
+      </c>
+      <c r="E50">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C51" t="str">
         <v>단독</v>
       </c>
-      <c r="C5" t="str">
-        <v>100M</v>
-      </c>
-      <c r="D5" t="str">
-        <v>없음</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>KT</v>
-      </c>
-      <c r="B6" t="str">
-        <v>결합</v>
-      </c>
-      <c r="C6" t="str">
-        <v>1G</v>
-      </c>
-      <c r="D6" t="str">
-        <v>지니TV 스탠다드</v>
-      </c>
-      <c r="E6">
+      <c r="D51" t="str">
+        <v>인터넷 100M</v>
+      </c>
+      <c r="E51">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
         <v>50</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LG</v>
-      </c>
-      <c r="B7" t="str">
+      <c r="B52" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C52" t="str">
         <v>단독</v>
       </c>
-      <c r="C7" t="str">
-        <v>500M</v>
-      </c>
-      <c r="D7" t="str">
-        <v>없음</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LG</v>
-      </c>
-      <c r="B8" t="str">
-        <v>결합</v>
-      </c>
-      <c r="C8" t="str">
-        <v>1G</v>
-      </c>
-      <c r="D8" t="str">
-        <v>U+tv 프리미엄</v>
-      </c>
-      <c r="E8">
+      <c r="D52" t="str">
+        <v>인터넷 500M</v>
+      </c>
+      <c r="E52">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C53" t="str">
+        <v>단독</v>
+      </c>
+      <c r="D53" t="str">
+        <v>인터넷 1G</v>
+      </c>
+      <c r="E53">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C54" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D54" t="str">
+        <v>인터넷 100M + U+tv 실속형</v>
+      </c>
+      <c r="E54">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C55" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D55" t="str">
+        <v>인터넷 100M + U+tv 기본형</v>
+      </c>
+      <c r="E55">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C56" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D56" t="str">
+        <v>인터넷 100M + U+tv 프리미엄</v>
+      </c>
+      <c r="E56">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
         <v>55</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="B57" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C57" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D57" t="str">
+        <v>인터넷 100M + U+tv 프리미엄 VOD</v>
+      </c>
+      <c r="E57">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C58" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D58" t="str">
+        <v>인터넷 500M + U+tv 실속형</v>
+      </c>
+      <c r="E58">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C59" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D59" t="str">
+        <v>인터넷 500M + U+tv 기본형</v>
+      </c>
+      <c r="E59">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C60" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D60" t="str">
+        <v>인터넷 500M + U+tv 프리미엄</v>
+      </c>
+      <c r="E60">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C61" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D61" t="str">
+        <v>인터넷 500M + U+tv 프리미엄 VOD</v>
+      </c>
+      <c r="E61">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C62" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D62" t="str">
+        <v>인터넷 1G + U+tv 실속형</v>
+      </c>
+      <c r="E62">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C63" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D63" t="str">
+        <v>인터넷 1G + U+tv 기본형</v>
+      </c>
+      <c r="E63">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C64" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D64" t="str">
+        <v>인터넷 1G + U+tv 프리미엄</v>
+      </c>
+      <c r="E64">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="str">
+        <v>LG U+</v>
+      </c>
+      <c r="C65" t="str">
+        <v>결합</v>
+      </c>
+      <c r="D65" t="str">
+        <v>인터넷 1G + U+tv 프리미엄 VOD</v>
+      </c>
+      <c r="E65">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>※ 인터넷+TV 사은품 정책은 통합 1개 (온·오프라인 공통) · 매장별 차등 없음 · 단위: 원</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -402,9 +402,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A28"/>
-  <cols>
-    <col min="1" max="1" width="90.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -556,16 +553,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H58"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -621,6 +608,12 @@
       <c r="F3">
         <v>45</v>
       </c>
+      <c r="G3">
+        <v>45</v>
+      </c>
+      <c r="H3">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -641,6 +634,12 @@
       <c r="F4">
         <v>45</v>
       </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -661,6 +660,12 @@
       <c r="F5">
         <v>45</v>
       </c>
+      <c r="G5">
+        <v>70</v>
+      </c>
+      <c r="H5">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -681,6 +686,12 @@
       <c r="F6">
         <v>45</v>
       </c>
+      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>70</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -701,6 +712,12 @@
       <c r="F7">
         <v>45</v>
       </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>120</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -721,6 +738,12 @@
       <c r="F8">
         <v>45</v>
       </c>
+      <c r="G8">
+        <v>35</v>
+      </c>
+      <c r="H8">
+        <v>45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -741,6 +764,12 @@
       <c r="F9">
         <v>45</v>
       </c>
+      <c r="G9">
+        <v>45</v>
+      </c>
+      <c r="H9">
+        <v>55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -761,6 +790,12 @@
       <c r="F10">
         <v>45</v>
       </c>
+      <c r="G10">
+        <v>65</v>
+      </c>
+      <c r="H10">
+        <v>80</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -781,6 +816,12 @@
       <c r="F11">
         <v>45</v>
       </c>
+      <c r="G11">
+        <v>55</v>
+      </c>
+      <c r="H11">
+        <v>70</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -801,6 +842,12 @@
       <c r="F12">
         <v>45</v>
       </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>35</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -821,6 +868,12 @@
       <c r="F13">
         <v>45</v>
       </c>
+      <c r="G13">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -841,6 +894,12 @@
       <c r="F14">
         <v>45</v>
       </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -861,6 +920,12 @@
       <c r="F15">
         <v>45</v>
       </c>
+      <c r="G15">
+        <v>55</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -881,6 +946,12 @@
       <c r="F16">
         <v>45</v>
       </c>
+      <c r="G16">
+        <v>75</v>
+      </c>
+      <c r="H16">
+        <v>95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -901,6 +972,12 @@
       <c r="F17">
         <v>45</v>
       </c>
+      <c r="G17">
+        <v>45</v>
+      </c>
+      <c r="H17">
+        <v>55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -921,6 +998,12 @@
       <c r="F18">
         <v>45</v>
       </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18">
+        <v>75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -941,6 +1024,12 @@
       <c r="F19">
         <v>45</v>
       </c>
+      <c r="G19">
+        <v>65</v>
+      </c>
+      <c r="H19">
+        <v>85</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -961,6 +1050,12 @@
       <c r="F20">
         <v>45</v>
       </c>
+      <c r="G20">
+        <v>80</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -981,6 +1076,12 @@
       <c r="F21">
         <v>50</v>
       </c>
+      <c r="G21">
+        <v>40</v>
+      </c>
+      <c r="H21">
+        <v>50</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1001,6 +1102,12 @@
       <c r="F22">
         <v>50</v>
       </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22">
+        <v>60</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1021,6 +1128,12 @@
       <c r="F23">
         <v>50</v>
       </c>
+      <c r="G23">
+        <v>65</v>
+      </c>
+      <c r="H23">
+        <v>85</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1041,6 +1154,12 @@
       <c r="F24">
         <v>50</v>
       </c>
+      <c r="G24">
+        <v>50</v>
+      </c>
+      <c r="H24">
+        <v>65</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1061,6 +1180,12 @@
       <c r="F25">
         <v>50</v>
       </c>
+      <c r="G25">
+        <v>90</v>
+      </c>
+      <c r="H25">
+        <v>115</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1081,6 +1206,12 @@
       <c r="F26">
         <v>50</v>
       </c>
+      <c r="G26">
+        <v>35</v>
+      </c>
+      <c r="H26">
+        <v>40</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1101,6 +1232,12 @@
       <c r="F27">
         <v>50</v>
       </c>
+      <c r="G27">
+        <v>40</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1121,6 +1258,12 @@
       <c r="F28">
         <v>50</v>
       </c>
+      <c r="G28">
+        <v>60</v>
+      </c>
+      <c r="H28">
+        <v>80</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1141,6 +1284,12 @@
       <c r="F29">
         <v>50</v>
       </c>
+      <c r="G29">
+        <v>50</v>
+      </c>
+      <c r="H29">
+        <v>65</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1161,6 +1310,12 @@
       <c r="F30">
         <v>50</v>
       </c>
+      <c r="G30">
+        <v>25</v>
+      </c>
+      <c r="H30">
+        <v>30</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1181,6 +1336,12 @@
       <c r="F31">
         <v>50</v>
       </c>
+      <c r="G31">
+        <v>40</v>
+      </c>
+      <c r="H31">
+        <v>50</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1201,6 +1362,12 @@
       <c r="F32">
         <v>50</v>
       </c>
+      <c r="G32">
+        <v>45</v>
+      </c>
+      <c r="H32">
+        <v>60</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1221,6 +1388,12 @@
       <c r="F33">
         <v>50</v>
       </c>
+      <c r="G33">
+        <v>55</v>
+      </c>
+      <c r="H33">
+        <v>70</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1241,6 +1414,12 @@
       <c r="F34">
         <v>50</v>
       </c>
+      <c r="G34">
+        <v>70</v>
+      </c>
+      <c r="H34">
+        <v>90</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1261,6 +1440,12 @@
       <c r="F35">
         <v>50</v>
       </c>
+      <c r="G35">
+        <v>40</v>
+      </c>
+      <c r="H35">
+        <v>50</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1281,6 +1466,12 @@
       <c r="F36">
         <v>50</v>
       </c>
+      <c r="G36">
+        <v>55</v>
+      </c>
+      <c r="H36">
+        <v>70</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1301,6 +1492,12 @@
       <c r="F37">
         <v>50</v>
       </c>
+      <c r="G37">
+        <v>65</v>
+      </c>
+      <c r="H37">
+        <v>80</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1320,6 +1517,12 @@
       </c>
       <c r="F38">
         <v>50</v>
+      </c>
+      <c r="G38">
+        <v>75</v>
+      </c>
+      <c r="H38">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -1341,6 +1544,12 @@
       <c r="F39">
         <v>47</v>
       </c>
+      <c r="G39">
+        <v>40</v>
+      </c>
+      <c r="H39">
+        <v>55</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1361,6 +1570,12 @@
       <c r="F40">
         <v>47</v>
       </c>
+      <c r="G40">
+        <v>50</v>
+      </c>
+      <c r="H40">
+        <v>65</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1381,6 +1596,12 @@
       <c r="F41">
         <v>47</v>
       </c>
+      <c r="G41">
+        <v>65</v>
+      </c>
+      <c r="H41">
+        <v>85</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1401,6 +1622,12 @@
       <c r="F42">
         <v>47</v>
       </c>
+      <c r="G42">
+        <v>50</v>
+      </c>
+      <c r="H42">
+        <v>65</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1421,6 +1648,12 @@
       <c r="F43">
         <v>47</v>
       </c>
+      <c r="G43">
+        <v>90</v>
+      </c>
+      <c r="H43">
+        <v>120</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1441,6 +1674,12 @@
       <c r="F44">
         <v>47</v>
       </c>
+      <c r="G44">
+        <v>35</v>
+      </c>
+      <c r="H44">
+        <v>45</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1461,6 +1700,12 @@
       <c r="F45">
         <v>47</v>
       </c>
+      <c r="G45">
+        <v>40</v>
+      </c>
+      <c r="H45">
+        <v>55</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1481,6 +1726,12 @@
       <c r="F46">
         <v>47</v>
       </c>
+      <c r="G46">
+        <v>60</v>
+      </c>
+      <c r="H46">
+        <v>80</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1501,6 +1752,12 @@
       <c r="F47">
         <v>47</v>
       </c>
+      <c r="G47">
+        <v>50</v>
+      </c>
+      <c r="H47">
+        <v>65</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1521,6 +1778,12 @@
       <c r="F48">
         <v>47</v>
       </c>
+      <c r="G48">
+        <v>25</v>
+      </c>
+      <c r="H48">
+        <v>30</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1541,6 +1804,12 @@
       <c r="F49">
         <v>47</v>
       </c>
+      <c r="G49">
+        <v>40</v>
+      </c>
+      <c r="H49">
+        <v>50</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1561,6 +1830,12 @@
       <c r="F50">
         <v>47</v>
       </c>
+      <c r="G50">
+        <v>45</v>
+      </c>
+      <c r="H50">
+        <v>60</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1581,6 +1856,12 @@
       <c r="F51">
         <v>47</v>
       </c>
+      <c r="G51">
+        <v>55</v>
+      </c>
+      <c r="H51">
+        <v>70</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -1601,6 +1882,12 @@
       <c r="F52">
         <v>47</v>
       </c>
+      <c r="G52">
+        <v>70</v>
+      </c>
+      <c r="H52">
+        <v>95</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -1621,6 +1908,12 @@
       <c r="F53">
         <v>47</v>
       </c>
+      <c r="G53">
+        <v>40</v>
+      </c>
+      <c r="H53">
+        <v>55</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -1641,6 +1934,12 @@
       <c r="F54">
         <v>47</v>
       </c>
+      <c r="G54">
+        <v>55</v>
+      </c>
+      <c r="H54">
+        <v>75</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -1661,6 +1960,12 @@
       <c r="F55">
         <v>47</v>
       </c>
+      <c r="G55">
+        <v>65</v>
+      </c>
+      <c r="H55">
+        <v>85</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -1680,6 +1985,12 @@
       </c>
       <c r="F56">
         <v>47</v>
+      </c>
+      <c r="G56">
+        <v>75</v>
+      </c>
+      <c r="H56">
+        <v>100</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -1703,6 +2014,12 @@
 ※ 할부 24개월 / 수수료 5.9% 원리금균등 (할부원금은 통신사 시스템 정책)
 ※ 공시지원금 ↔ 선택약정 동시 적용 불가 (택1)</v>
       </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1714,12 +2031,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D13"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1884,14 +2195,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E66"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>51</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="J3">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>71</v>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="J4">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>105</v>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="J5">
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>86</v>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
+      <c r="J6">
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>183</v>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>110</v>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="J8">
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>25</v>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>54</v>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10">
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>92</v>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11">
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>104</v>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="J12">
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>128</v>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
+      <c r="J13">
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="H14">
+        <v>60</v>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14">
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>80</v>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
+      <c r="J15">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="H16">
+        <v>114</v>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="J16">
+        <v>109</v>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="H17">
+        <v>75</v>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="J17">
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
+      <c r="H18">
+        <v>169</v>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18">
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
+      <c r="H19">
+        <v>80</v>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
+      <c r="H20">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
+      <c r="J20">
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21" t="str">
-        <v/>
+      <c r="H21">
+        <v>57</v>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="J21">
+        <v>90</v>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>92</v>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="J22">
+        <v>117</v>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>112</v>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="J23">
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>131.1</v>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
+      <c r="J24">
+        <v>160.1</v>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>41</v>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="J25">
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>61</v>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="J26">
+        <v>63</v>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>95</v>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="J27">
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>75</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="J28">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>164</v>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="J29">
+        <v>155</v>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>54</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="J30">
+        <v>75</v>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>13</v>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="J31">
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>23</v>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="J32">
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>42</v>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="J33">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>17</v>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
+      <c r="J34">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35" t="str">
-        <v/>
+      <c r="H35">
+        <v>92</v>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
+      <c r="J35">
+        <v>128</v>
       </c>
     </row>
     <row r="36">
@@ -1726,18 +1726,45 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>121.4</v>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
+      <c r="J36">
+        <v>147.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
@@ -1745,39 +1772,255 @@
       <c r="A38" t="str">
         <v>※ G(번이 공시현금가)·H(번이 선약현금가)·I(기변 공시현금가)·J(기변 선약현금가) — 매장이 직접 입력 (만원·음수 허용)</v>
       </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v>※ K~N 매장지원금(=봉이지원금)은 G~J 입력 시 자동 계산</v>
       </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>※ 자동 계산:</v>
       </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">  · K (번이 공시 매장지원금) = D − F − G</v>
       </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">  · L (번이 선약 매장지원금) = D − H  (공시 0)</v>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">  · M (기변 공시 매장지원금) = D − F − I</v>
       </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">  · N (기변 선약 매장지원금) = D − J  (공시 0)</v>
       </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
@@ -1785,19 +2028,127 @@
       <c r="A46" t="str">
         <v>※ 봉이 거래 공식 (공시 케이스 — F 사용):</v>
       </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">  · 현금: 출고가 − 공시지원금 − 매장지원금 = 공시현금가</v>
       </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">  · 할부: 할부원금 = 출고가 − 공시지원금 − 매장지원금  →  ÷ 24개월 (월 할부)</v>
       </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
         <v/>
       </c>
     </row>
@@ -1805,19 +2156,127 @@
       <c r="A50" t="str">
         <v>※ 봉이 거래 공식 (선택약정 25% 케이스 — F 미사용):</v>
       </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
         <v xml:space="preserve">  · 현금: 출고가 − 매장지원금 = 선약현금가 (공시 없음)</v>
       </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
         <v xml:space="preserve">  · 할부: 할부원금 = 출고가 − 매장지원금  →  ÷ 24개월 (월 할부 + 월요금 25%↓)</v>
       </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
         <v/>
       </c>
     </row>
@@ -1825,25 +2284,160 @@
       <c r="A54" t="str">
         <v>※ 2026-05-31 정책 변경: 할부 페이백 폐기 → 할부원금 직접 차감</v>
       </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v>※ 할부 24개월 / 수수료 5.9% 원리금균등</v>
       </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v>※ 공시지원금 ↔ 선택약정 25% 동시 적용 불가 (택1)</v>
       </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
         <v>※ 현금가 ≤ 0 (기기값 0원 + 페이백) = 할부 차단·현금 개통만 가능</v>
       </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
         <v>※ Upsert PK: (통신사 + 펫네임 + 용량 + 요금제)</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3">
-        <v>51</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3">
-        <v>60</v>
+      <c r="J3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4">
-        <v>71</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4">
-        <v>80</v>
+      <c r="J4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5">
-        <v>105</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5">
-        <v>114</v>
+      <c r="J5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6">
-        <v>86</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6">
-        <v>122</v>
+      <c r="J6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7">
-        <v>183</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7">
-        <v>206</v>
+      <c r="J7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8">
-        <v>110</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8">
-        <v>105</v>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9">
-        <v>25</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>56</v>
+      <c r="J9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10">
-        <v>54</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10">
-        <v>106</v>
+      <c r="J10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11">
-        <v>92</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11">
-        <v>134</v>
+      <c r="J11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12">
-        <v>104</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12">
-        <v>156</v>
+      <c r="J12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13">
-        <v>128</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13">
-        <v>175</v>
+      <c r="J13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14">
-        <v>60</v>
+      <c r="H14" t="str">
+        <v/>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14">
-        <v>55</v>
+      <c r="J14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15">
-        <v>80</v>
+      <c r="H15" t="str">
+        <v/>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15">
-        <v>75</v>
+      <c r="J15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16">
-        <v>114</v>
+      <c r="H16" t="str">
+        <v/>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16">
-        <v>109</v>
+      <c r="J16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17">
-        <v>75</v>
+      <c r="H17" t="str">
+        <v/>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17">
-        <v>92</v>
+      <c r="J17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18">
-        <v>169</v>
+      <c r="H18" t="str">
+        <v/>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18">
-        <v>178</v>
+      <c r="J18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19">
-        <v>80</v>
+      <c r="H19" t="str">
+        <v/>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19">
-        <v>85</v>
+      <c r="J19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20">
-        <v>17</v>
+      <c r="H20" t="str">
+        <v/>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20">
-        <v>39</v>
+      <c r="J20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21">
-        <v>57</v>
+      <c r="H21" t="str">
+        <v/>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21">
-        <v>90</v>
+      <c r="J21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22">
-        <v>92</v>
+      <c r="H22" t="str">
+        <v/>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22">
-        <v>117</v>
+      <c r="J22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23">
-        <v>112</v>
+      <c r="H23" t="str">
+        <v/>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23">
-        <v>141</v>
+      <c r="J23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24">
-        <v>131.1</v>
+      <c r="H24" t="str">
+        <v/>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24">
-        <v>160.1</v>
+      <c r="J24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25">
-        <v>41</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25">
-        <v>43</v>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26">
-        <v>61</v>
+      <c r="H26" t="str">
+        <v/>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26">
-        <v>63</v>
+      <c r="J26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27">
-        <v>95</v>
+      <c r="H27" t="str">
+        <v/>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27">
-        <v>97</v>
+      <c r="J27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28">
-        <v>75</v>
+      <c r="H28" t="str">
+        <v/>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28">
-        <v>64</v>
+      <c r="J28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29">
-        <v>164</v>
+      <c r="H29" t="str">
+        <v/>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29">
-        <v>155</v>
+      <c r="J29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30">
-        <v>54</v>
+      <c r="H30" t="str">
+        <v/>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30">
-        <v>75</v>
+      <c r="J30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31">
-        <v>13</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31">
-        <v>46</v>
+      <c r="J31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32">
-        <v>23</v>
+      <c r="H32" t="str">
+        <v/>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32">
-        <v>73</v>
+      <c r="J32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33">
-        <v>42</v>
+      <c r="H33" t="str">
+        <v/>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33">
-        <v>78</v>
+      <c r="J33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34">
-        <v>17</v>
+      <c r="H34" t="str">
+        <v/>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34">
-        <v>108</v>
+      <c r="J34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35">
-        <v>92</v>
+      <c r="H35" t="str">
+        <v/>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35">
-        <v>128</v>
+      <c r="J35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1726,14 +1726,14 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36">
-        <v>121.4</v>
+      <c r="H36" t="str">
+        <v/>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36">
-        <v>147.4</v>
+      <c r="J36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1802,193 +1802,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>※ K~N 매장지원금(=봉이지원금)은 G~J 입력 시 자동 계산</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39" t="str">
-        <v/>
+        <v>※ 선약현금가는 매장이 직접 입력 (공시지원금 + 공시현금가 공식은 매장지원금 차이에 따라 부정확)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>※ 자동 계산:</v>
-      </c>
-      <c r="B40" t="str">
-        <v/>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-      <c r="J40" t="str">
-        <v/>
+        <v>※ G·H·I·J 모두 매장이 직접 입력 (자동 계산 없음)</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  · K (번이 공시 매장지원금) = D − F − G</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="J41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">  · L (번이 선약 매장지원금) = D − H  (공시 0)</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
-      </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  · M (기변 공시 매장지원금) = D − F − I</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  · N (기변 선약 매장지원금) = D − J  (공시 0)</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="J44" t="str">
         <v/>
       </c>
     </row>

--- a/docs/template-form.xlsx
+++ b/docs/template-form.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>51</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="J3">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>71</v>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="J4">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>105</v>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="J5">
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>86</v>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
+      <c r="J6">
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>183</v>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>110</v>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="J8">
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>25</v>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>54</v>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10">
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>92</v>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11">
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>104</v>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="J12">
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>128</v>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
+      <c r="J13">
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="H14">
+        <v>60</v>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14">
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>80</v>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
+      <c r="J15">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="H16">
+        <v>114</v>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="J16">
+        <v>109</v>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="H17">
+        <v>75</v>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="J17">
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
+      <c r="H18">
+        <v>169</v>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18">
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
+      <c r="H19">
+        <v>80</v>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
+      <c r="H20">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
+      <c r="J20">
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21" t="str">
-        <v/>
+      <c r="H21">
+        <v>57</v>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="J21">
+        <v>90</v>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>92</v>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="J22">
+        <v>117</v>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>112</v>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="J23">
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>131.1</v>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
+      <c r="J24">
+        <v>160.1</v>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>41</v>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="J25">
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>61</v>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="J26">
+        <v>63</v>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>95</v>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="J27">
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>75</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="J28">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>164</v>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="J29">
+        <v>155</v>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>54</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="J30">
+        <v>75</v>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>13</v>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="J31">
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>23</v>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="J32">
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>42</v>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="J33">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>17</v>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
+      <c r="J34">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35" t="str">
-        <v/>
+      <c r="H35">
+        <v>92</v>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
+      <c r="J35">
+        <v>128</v>
       </c>
     </row>
     <row r="36">
@@ -1726,14 +1726,14 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>121.4</v>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
+      <c r="J36">
+        <v>147.4</v>
       </c>
     </row>
     <row r="37">
@@ -1804,29 +1804,191 @@
       <c r="A39" t="str">
         <v>※ 선약현금가는 매장이 직접 입력 (공시지원금 + 공시현금가 공식은 매장지원금 차이에 따라 부정확)</v>
       </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>※ G·H·I·J 모두 매장이 직접 입력 (자동 계산 없음)</v>
       </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v/>
       </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v/>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v/>
       </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
